--- a/cbb_model.xlsx
+++ b/cbb_model.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23640" windowHeight="15540" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15540" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="data_1_10_14" sheetId="8" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Sheet1" sheetId="9" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">data_1_10_14!$F$2:$F$200</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">data_1_10_14!$F$2:$F$122</definedName>
     <definedName name="solver_adj" localSheetId="2" hidden="1">data_1_5_14!$G$2:$G$144</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">data_1_6_14!$G$2:$G$197</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
@@ -29,7 +29,7 @@
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">data_1_10_14!$F$2:$F$200</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">data_1_10_14!$F$2:$F$122</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">data_1_5_14!$G$2:$G$144</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">data_1_6_14!$G$2:$G$197</definedName>
     <definedName name="solver_lhs10" localSheetId="0" hidden="1">data_1_10_14!$F$4</definedName>
@@ -38,16 +38,16 @@
     <definedName name="solver_lhs11" localSheetId="0" hidden="1">data_1_10_14!#REF!</definedName>
     <definedName name="solver_lhs11" localSheetId="2" hidden="1">data_1_5_14!#REF!</definedName>
     <definedName name="solver_lhs11" localSheetId="1" hidden="1">data_1_6_14!#REF!</definedName>
-    <definedName name="solver_lhs12" localSheetId="0" hidden="1">data_1_10_14!$N$2</definedName>
+    <definedName name="solver_lhs12" localSheetId="0" hidden="1">data_1_10_14!$O$2</definedName>
     <definedName name="solver_lhs12" localSheetId="2" hidden="1">data_1_5_14!$O$2</definedName>
     <definedName name="solver_lhs12" localSheetId="1" hidden="1">data_1_6_14!$O$2</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">data_1_10_14!$L$2</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">data_1_10_14!$M$2</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">data_1_5_14!$M$2</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">data_1_6_14!$M$2</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">data_1_10_14!$M$2</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">data_1_10_14!$N$2</definedName>
     <definedName name="solver_lhs3" localSheetId="2" hidden="1">data_1_5_14!$N$2</definedName>
     <definedName name="solver_lhs3" localSheetId="1" hidden="1">data_1_6_14!$N$2</definedName>
-    <definedName name="solver_lhs4" localSheetId="0" hidden="1">data_1_10_14!$N$2</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">data_1_10_14!$O$2</definedName>
     <definedName name="solver_lhs4" localSheetId="2" hidden="1">data_1_5_14!$O$2</definedName>
     <definedName name="solver_lhs4" localSheetId="1" hidden="1">data_1_6_14!$O$2</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">data_1_10_14!#REF!</definedName>
@@ -89,7 +89,7 @@
     <definedName name="solver_num" localSheetId="0" hidden="1">4</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">4</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">4</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">data_1_10_14!$O$2</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">data_1_10_14!$P$2</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">data_1_5_14!$P$2</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">data_1_6_14!$P$2</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="505">
   <si>
     <t>G</t>
   </si>
@@ -1691,9 +1691,6 @@
     <t>33.124.520.620.210.817.424.829.325.932.17.219.216.822.2</t>
   </si>
   <si>
-    <t>Austin Nichols</t>
-  </si>
-  <si>
     <t>Gary Payton II</t>
   </si>
   <si>
@@ -1706,18 +1703,12 @@
     <t>Stanley Johnson</t>
   </si>
   <si>
-    <t>Markus Kennedy</t>
-  </si>
-  <si>
     <t>Kevon Looney</t>
   </si>
   <si>
     <t>Bryce Alford</t>
   </si>
   <si>
-    <t>Myles Mack</t>
-  </si>
-  <si>
     <t>Rondae Hollis-Jefferson</t>
   </si>
   <si>
@@ -1727,39 +1718,18 @@
     <t>Anthony Brown</t>
   </si>
   <si>
-    <t>Ben Moore</t>
-  </si>
-  <si>
-    <t>Kadeem Jack</t>
-  </si>
-  <si>
-    <t>Nic Moore</t>
-  </si>
-  <si>
     <t>T.J. McConnell</t>
   </si>
   <si>
-    <t>Shaq Goodwin</t>
-  </si>
-  <si>
-    <t>Yanick Moreira</t>
-  </si>
-  <si>
     <t>Langston Morris-Walker</t>
   </si>
   <si>
-    <t>Trashon Burrell</t>
-  </si>
-  <si>
     <t>Brandon Ashley</t>
   </si>
   <si>
     <t>Olaf Schaftenaar</t>
   </si>
   <si>
-    <t>Keith Frazier</t>
-  </si>
-  <si>
     <t>Kaleb Tarczewski</t>
   </si>
   <si>
@@ -1769,66 +1739,27 @@
     <t>Jarmal Reid</t>
   </si>
   <si>
-    <t>Greg Lewis</t>
-  </si>
-  <si>
     <t>Tony Parker</t>
   </si>
   <si>
-    <t>Cannen Cunningham</t>
-  </si>
-  <si>
-    <t>Junior Etou</t>
-  </si>
-  <si>
     <t>Malcolm Duvivier</t>
   </si>
   <si>
     <t>Victor Robbins</t>
   </si>
   <si>
-    <t>Avery Woodson</t>
-  </si>
-  <si>
-    <t>Justin Martin</t>
-  </si>
-  <si>
-    <t>D'Marnier Cunningham</t>
-  </si>
-  <si>
-    <t>Ben Emelogu</t>
-  </si>
-  <si>
-    <t>Ryan Manuel</t>
-  </si>
-  <si>
-    <t>Mike Williams</t>
-  </si>
-  <si>
     <t>Gabe York</t>
   </si>
   <si>
     <t>Rosco Allen</t>
   </si>
   <si>
-    <t>Nick King</t>
-  </si>
-  <si>
-    <t>Pookie Powell</t>
-  </si>
-  <si>
     <t>Matt Dahlen</t>
   </si>
   <si>
     <t>Tanner Sanders</t>
   </si>
   <si>
-    <t>D.J. Foreman</t>
-  </si>
-  <si>
-    <t>Shaquille Doorson</t>
-  </si>
-  <si>
     <t>Dusan Ristic</t>
   </si>
   <si>
@@ -1847,48 +1778,24 @@
     <t>Thomas Welsh</t>
   </si>
   <si>
-    <t>Kerwin Okoro</t>
-  </si>
-  <si>
     <t>Grant Verhoeven</t>
   </si>
   <si>
-    <t>Calvin Godfrey</t>
-  </si>
-  <si>
-    <t>Bishop Daniels</t>
-  </si>
-  <si>
-    <t>Kedren Johnson</t>
-  </si>
-  <si>
     <t>Daniel Gomis</t>
   </si>
   <si>
-    <t>Malick Kone</t>
-  </si>
-  <si>
-    <t>Chris Hawkins</t>
-  </si>
-  <si>
     <t>Noah Allen</t>
   </si>
   <si>
     <t>Marcus Allen</t>
   </si>
   <si>
-    <t>Sterling Brown</t>
-  </si>
-  <si>
     <t>Cheikh N'diaye</t>
   </si>
   <si>
     <t>Wanaah Bail</t>
   </si>
   <si>
-    <t>Markel Crawford</t>
-  </si>
-  <si>
     <t>Elliott Pitts</t>
   </si>
   <si>
@@ -1898,84 +1805,30 @@
     <t>Tyrone Wallace</t>
   </si>
   <si>
-    <t>Frank Kaminsky</t>
-  </si>
-  <si>
-    <t>Jahlil Okafor</t>
-  </si>
-  <si>
     <t>Rakeem Christmas</t>
   </si>
   <si>
-    <t>Jherrod Stiggers</t>
-  </si>
-  <si>
-    <t>Trevor Lacey</t>
-  </si>
-  <si>
-    <t>Justise Winslow</t>
-  </si>
-  <si>
-    <t>Nigel Hayes</t>
-  </si>
-  <si>
-    <t>L.J. Rose</t>
-  </si>
-  <si>
     <t>Chris McCullough</t>
   </si>
   <si>
-    <t>Devonta Pollard</t>
-  </si>
-  <si>
     <t>Jordan Mathews</t>
   </si>
   <si>
-    <t>Jonathan Stark</t>
-  </si>
-  <si>
     <t>David Kravish</t>
   </si>
   <si>
-    <t>Quinn Cook</t>
-  </si>
-  <si>
     <t>Michael Gbinije</t>
   </si>
   <si>
-    <t>Brandon Goodwin</t>
-  </si>
-  <si>
     <t>Malcolm Hill</t>
   </si>
   <si>
     <t>Nikola Jovanovic</t>
   </si>
   <si>
-    <t>Adonys Henriquez</t>
-  </si>
-  <si>
-    <t>Jordan McLaughlin</t>
-  </si>
-  <si>
     <t>Trevor Cooney</t>
   </si>
   <si>
-    <t>B.J. Taylor</t>
-  </si>
-  <si>
-    <t>Tyus Jones</t>
-  </si>
-  <si>
-    <t>Sam Dekker</t>
-  </si>
-  <si>
-    <t>Anthony Barber</t>
-  </si>
-  <si>
-    <t>Danrad Knowles</t>
-  </si>
-  <si>
     <t>Kaleb Joseph</t>
   </si>
   <si>
@@ -1985,105 +1838,33 @@
     <t>Nnanna Egwu</t>
   </si>
   <si>
-    <t>Kyle Washington</t>
-  </si>
-  <si>
-    <t>Ralston Turner</t>
-  </si>
-  <si>
-    <t>Traevon Jackson</t>
-  </si>
-  <si>
-    <t>Rasheed Sulaimon</t>
-  </si>
-  <si>
-    <t>Louis Dabney</t>
-  </si>
-  <si>
-    <t>Amile Jefferson</t>
-  </si>
-  <si>
-    <t>Dylan Osetkowski</t>
-  </si>
-  <si>
     <t>Katin Reinhardt</t>
   </si>
   <si>
-    <t>Justin McBride</t>
-  </si>
-  <si>
     <t>Reid Travis</t>
   </si>
   <si>
-    <t>Jay Hook</t>
-  </si>
-  <si>
-    <t>Eric Weary</t>
-  </si>
-  <si>
     <t>Kendrick Nunn</t>
   </si>
   <si>
     <t>Darion Clark</t>
   </si>
   <si>
-    <t>LeRon Barnes</t>
-  </si>
-  <si>
-    <t>Josh Gasser</t>
-  </si>
-  <si>
     <t>Tyler Roberson</t>
   </si>
   <si>
     <t>Robbie Berwick</t>
   </si>
   <si>
-    <t>Kasey Wilson</t>
-  </si>
-  <si>
-    <t>Tre Drye</t>
-  </si>
-  <si>
-    <t>Daiquan Walker</t>
-  </si>
-  <si>
-    <t>Matt Jones</t>
-  </si>
-  <si>
     <t>Ahmad Starks</t>
   </si>
   <si>
-    <t>Kajon Mack</t>
-  </si>
-  <si>
     <t>Aaron Cosby</t>
   </si>
   <si>
-    <t>Shaheed Davis</t>
-  </si>
-  <si>
-    <t>Abu Abdul-Malik</t>
-  </si>
-  <si>
-    <t>Caleb Martin</t>
-  </si>
-  <si>
-    <t>Keith Pinckney</t>
-  </si>
-  <si>
-    <t>Grayson Allen</t>
-  </si>
-  <si>
-    <t>Khalil Batie</t>
-  </si>
-  <si>
     <t>Dayshawn Watkins</t>
   </si>
   <si>
-    <t>Cody Martin</t>
-  </si>
-  <si>
     <t>Brandon Chauca</t>
   </si>
   <si>
@@ -2096,87 +1877,33 @@
     <t>Elijah Stewart</t>
   </si>
   <si>
-    <t>Troy Holston Jr.</t>
-  </si>
-  <si>
-    <t>Dinero Mercurius</t>
-  </si>
-  <si>
-    <t>Jaleel Cousins</t>
-  </si>
-  <si>
     <t>Leron Black</t>
   </si>
   <si>
-    <t>Wes VanBeck</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Egi Gjikondi</t>
-  </si>
-  <si>
-    <t>J.C. Washington</t>
-  </si>
-  <si>
-    <t>Staphon Blair</t>
-  </si>
-  <si>
-    <t>Dylan Karell</t>
-  </si>
-  <si>
-    <t>Matt Williams</t>
-  </si>
-  <si>
     <t>Leslee Smith</t>
   </si>
   <si>
-    <t>Adam Drexler</t>
-  </si>
-  <si>
-    <t>Cavon Baker</t>
-  </si>
-  <si>
     <t>Michael Ojo</t>
   </si>
   <si>
     <t>Strahinja Gavrilovic</t>
   </si>
   <si>
-    <t>Mikhail McLean</t>
-  </si>
-  <si>
     <t>Christian Behrens</t>
   </si>
   <si>
-    <t>Marshall Plumlee</t>
-  </si>
-  <si>
     <t>Dwight Tarwater</t>
   </si>
   <si>
-    <t>Duje Dukan</t>
-  </si>
-  <si>
-    <t>Dre' Clayton</t>
-  </si>
-  <si>
     <t>Chass Bryan</t>
   </si>
   <si>
-    <t>Kuran Iverson</t>
-  </si>
-  <si>
     <t>B.J. Johnson</t>
   </si>
   <si>
     <t>Sam Singer</t>
   </si>
   <si>
-    <t>Jabari Bird</t>
-  </si>
-  <si>
     <t>Roger Moute a Bidias</t>
   </si>
   <si>
@@ -2186,46 +1913,94 @@
     <t>Ron Patterson</t>
   </si>
   <si>
-    <t>Ryan Smith</t>
-  </si>
-  <si>
-    <t>Josh Hearlihy</t>
-  </si>
-  <si>
-    <t>Payton Henson</t>
-  </si>
-  <si>
-    <t>Cameron Reynolds</t>
-  </si>
-  <si>
-    <t>Chase Cannon</t>
-  </si>
-  <si>
-    <t>Patrick Wallace</t>
-  </si>
-  <si>
     <t>Austin Colbert</t>
   </si>
   <si>
     <t>Maverick Morgan</t>
   </si>
   <si>
-    <t>Desmond Lee</t>
-  </si>
-  <si>
-    <t>Lennard Freeman</t>
-  </si>
-  <si>
-    <t>Beejay Anya</t>
-  </si>
-  <si>
     <t>Jaylon Tate</t>
   </si>
   <si>
-    <t>Bronson Koenig</t>
-  </si>
-  <si>
-    <t>Vitto Brown</t>
+    <t>Dylan Livesay</t>
+  </si>
+  <si>
+    <t>AJ Hedgecock</t>
+  </si>
+  <si>
+    <t>Cameron Liss</t>
+  </si>
+  <si>
+    <t>Justin Stangel</t>
+  </si>
+  <si>
+    <t>Alec Wulff</t>
+  </si>
+  <si>
+    <t>Mike Sutton</t>
+  </si>
+  <si>
+    <t>Cole Welle</t>
+  </si>
+  <si>
+    <t>Dorian Pickens</t>
+  </si>
+  <si>
+    <t>Nick Hamilton</t>
+  </si>
+  <si>
+    <t>Michael Saxton</t>
+  </si>
+  <si>
+    <t>Doyin Akintobi-Adeyeye</t>
+  </si>
+  <si>
+    <t>Mike LaTulip</t>
+  </si>
+  <si>
+    <t>Kory Alford</t>
+  </si>
+  <si>
+    <t>Carter Sanderson</t>
+  </si>
+  <si>
+    <t>Jacob Hazzard</t>
+  </si>
+  <si>
+    <t>Matt Korcheck</t>
+  </si>
+  <si>
+    <t>Christian Sanders</t>
+  </si>
+  <si>
+    <t>Drew Mellon</t>
+  </si>
+  <si>
+    <t>Wade Morgan</t>
+  </si>
+  <si>
+    <t>Nick Kazemi</t>
+  </si>
+  <si>
+    <t>Trey Mason</t>
+  </si>
+  <si>
+    <t>Kahlil Dukes</t>
+  </si>
+  <si>
+    <t>Kameron Rooks</t>
+  </si>
+  <si>
+    <t>Samer Dhillon</t>
+  </si>
+  <si>
+    <t>Brandon Allen</t>
+  </si>
+  <si>
+    <t>Elliott Bullock</t>
+  </si>
+  <si>
+    <t>Brenden Glapion</t>
   </si>
 </sst>
 </file>
@@ -2713,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O574"/>
+  <dimension ref="A1:P496"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="5"/>
@@ -2723,7 +2498,7 @@
     <col min="10" max="11" width="10.83203125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>157</v>
       </c>
@@ -2734,7 +2509,7 @@
         <v>156</v>
       </c>
       <c r="D1" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>159</v>
@@ -2757,92 +2532,92 @@
       <c r="K1" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>164</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>165</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>155</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>489</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>25.25</v>
+        <v>31.19</v>
       </c>
       <c r="D2">
-        <v>24.01</v>
+        <v>31.36</v>
       </c>
       <c r="E2" s="3">
-        <v>6300</v>
-      </c>
-      <c r="F2" s="15">
+        <v>8300</v>
+      </c>
+      <c r="F2" s="13">
         <v>1</v>
       </c>
       <c r="G2" s="13">
         <f>IF(A2="G",1,0)*F2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="13">
         <f>IF(A2="F",1,0)*F2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="16">
         <f>E2/D2</f>
-        <v>262.39067055393582</v>
+        <v>264.66836734693879</v>
       </c>
       <c r="J2" s="17">
         <f>E2*F2</f>
-        <v>6300</v>
+        <v>8300</v>
       </c>
       <c r="K2" s="13">
         <f>F2*D2</f>
-        <v>24.01</v>
-      </c>
-      <c r="L2">
-        <f>SUM(H2:H119)</f>
+        <v>31.36</v>
+      </c>
+      <c r="M2">
+        <f>SUM(H2:H298)</f>
         <v>5</v>
       </c>
-      <c r="M2">
-        <f>SUM(G2:G119)</f>
+      <c r="N2">
+        <f>SUM(G2:G298)</f>
         <v>4</v>
       </c>
-      <c r="N2" s="3">
-        <f>SUM(J2:J119)</f>
+      <c r="O2" s="3">
+        <f>SUM(J2:J298)</f>
         <v>60000</v>
       </c>
-      <c r="O2">
-        <f>SUM(K2:K119)</f>
-        <v>219.15999999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="16">
+      <c r="P2">
+        <f>SUM(K2:K2298)</f>
+        <v>213.63000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>445</v>
       </c>
       <c r="C3">
-        <v>31.19</v>
+        <v>23.66</v>
       </c>
       <c r="D3">
-        <v>31.5</v>
+        <v>24.2</v>
       </c>
       <c r="E3" s="3">
-        <v>8300</v>
-      </c>
-      <c r="F3" s="15">
+        <v>6500</v>
+      </c>
+      <c r="F3" s="13">
         <v>1</v>
       </c>
       <c r="G3" s="13">
@@ -2855,34 +2630,34 @@
       </c>
       <c r="I3" s="16">
         <f>E3/D3</f>
-        <v>263.49206349206349</v>
+        <v>268.59504132231405</v>
       </c>
       <c r="J3" s="17">
         <f>E3*F3</f>
-        <v>8300</v>
+        <v>6500</v>
       </c>
       <c r="K3" s="13">
         <f>F3*D3</f>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="16">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="C4">
-        <v>26.32</v>
+        <v>36.340000000000003</v>
       </c>
       <c r="D4">
-        <v>27.27</v>
+        <v>34.43</v>
       </c>
       <c r="E4" s="3">
-        <v>7300</v>
-      </c>
-      <c r="F4" s="15">
+        <v>9300</v>
+      </c>
+      <c r="F4" s="13">
         <v>1</v>
       </c>
       <c r="G4" s="13">
@@ -2895,155 +2670,155 @@
       </c>
       <c r="I4" s="16">
         <f>E4/D4</f>
-        <v>267.6934360102677</v>
+        <v>270.11327330816147</v>
       </c>
       <c r="J4" s="17">
         <f>E4*F4</f>
-        <v>7300</v>
+        <v>9300</v>
       </c>
       <c r="K4" s="13">
         <f>F4*D4</f>
-        <v>27.27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="16">
+        <v>34.43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="C5">
-        <v>26.79</v>
+        <v>33.85</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>31.26</v>
       </c>
       <c r="E5" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F5" s="15">
+        <v>8600</v>
+      </c>
+      <c r="F5" s="13">
         <v>1</v>
       </c>
       <c r="G5" s="13">
         <f>IF(A5="G",1,0)*F5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="13">
         <f>IF(A5="F",1,0)*F5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="16">
         <f>E5/D5</f>
-        <v>273.07692307692309</v>
+        <v>275.1119641714651</v>
       </c>
       <c r="J5" s="17">
         <f>E5*F5</f>
-        <v>7100</v>
+        <v>8600</v>
       </c>
       <c r="K5" s="13">
         <f>F5*D5</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="16">
+        <v>31.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="C6">
-        <v>23.57</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="D6">
-        <v>24.82</v>
+        <v>18.82</v>
       </c>
       <c r="E6" s="3">
-        <v>6800</v>
-      </c>
-      <c r="F6" s="15">
+        <v>5300</v>
+      </c>
+      <c r="F6" s="13">
         <v>1</v>
       </c>
       <c r="G6" s="13">
         <f>IF(A6="G",1,0)*F6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="13">
         <f>IF(A6="F",1,0)*F6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="16">
         <f>E6/D6</f>
-        <v>273.97260273972603</v>
+        <v>281.61530286928797</v>
       </c>
       <c r="J6" s="17">
         <f>E6*F6</f>
-        <v>6800</v>
+        <v>5300</v>
       </c>
       <c r="K6" s="13">
         <f>F6*D6</f>
-        <v>24.82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="16">
+        <v>18.82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>487</v>
+        <v>415</v>
       </c>
       <c r="C7">
-        <v>23.66</v>
+        <v>19.04</v>
       </c>
       <c r="D7">
-        <v>23.51</v>
+        <v>19.89</v>
       </c>
       <c r="E7" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F7" s="15">
+        <v>5700</v>
+      </c>
+      <c r="F7" s="13">
         <v>1</v>
       </c>
       <c r="G7" s="13">
         <f>IF(A7="G",1,0)*F7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="13">
         <f>IF(A7="F",1,0)*F7</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="16">
         <f>E7/D7</f>
-        <v>276.47809442790299</v>
+        <v>286.57616892911011</v>
       </c>
       <c r="J7" s="17">
         <f>E7*F7</f>
-        <v>6500</v>
+        <v>5700</v>
       </c>
       <c r="K7" s="13">
         <f>F7*D7</f>
-        <v>23.51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="16">
+        <v>19.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>562</v>
+        <v>417</v>
       </c>
       <c r="C8">
-        <v>17.95</v>
+        <v>22.01</v>
       </c>
       <c r="D8">
-        <v>16.260000000000002</v>
+        <v>21.47</v>
       </c>
       <c r="E8" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F8" s="15">
-        <v>0</v>
+        <v>6200</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1</v>
       </c>
       <c r="G8" s="13">
         <f>IF(A8="G",1,0)*F8</f>
@@ -3051,83 +2826,83 @@
       </c>
       <c r="H8" s="13">
         <f>IF(A8="F",1,0)*F8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="16">
         <f>E8/D8</f>
-        <v>276.75276752767525</v>
+        <v>288.77503493246394</v>
       </c>
       <c r="J8" s="17">
         <f>E8*F8</f>
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="K8" s="13">
         <f>F8*D8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="16">
+        <v>21.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C9">
-        <v>18.61</v>
+        <v>16.5</v>
       </c>
       <c r="D9">
-        <v>16.13</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="E9" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F9" s="15">
+        <v>5100</v>
+      </c>
+      <c r="F9" s="13">
         <v>1</v>
       </c>
       <c r="G9" s="13">
         <f>IF(A9="G",1,0)*F9</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="13">
         <f>IF(A9="F",1,0)*F9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="16">
         <f>E9/D9</f>
-        <v>278.98326100433974</v>
+        <v>304.65949820788535</v>
       </c>
       <c r="J9" s="17">
         <f>E9*F9</f>
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="K9" s="13">
         <f>F9*D9</f>
-        <v>16.13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="16">
+        <v>16.739999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>469</v>
+        <v>419</v>
       </c>
       <c r="C10">
-        <v>36.340000000000003</v>
+        <v>16.71</v>
       </c>
       <c r="D10">
-        <v>33.270000000000003</v>
+        <v>15.46</v>
       </c>
       <c r="E10" s="3">
-        <v>9300</v>
-      </c>
-      <c r="F10" s="15">
-        <v>0</v>
+        <v>5000</v>
+      </c>
+      <c r="F10" s="13">
+        <v>1</v>
       </c>
       <c r="G10" s="13">
         <f>IF(A10="G",1,0)*F10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="13">
         <f>IF(A10="F",1,0)*F10</f>
@@ -3135,35 +2910,35 @@
       </c>
       <c r="I10" s="16">
         <f>E10/D10</f>
-        <v>279.53110910730385</v>
+        <v>323.41526520051747</v>
       </c>
       <c r="J10" s="17">
         <f>E10*F10</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K10" s="13">
         <f>F10*D10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="16">
+        <v>15.46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="C11">
-        <v>17.36</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
-        <v>17.88</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F11" s="15">
-        <v>1</v>
+        <v>4500</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
       </c>
       <c r="G11" s="13">
         <f>IF(A11="G",1,0)*F11</f>
@@ -3171,38 +2946,38 @@
       </c>
       <c r="H11" s="13">
         <f>IF(A11="F",1,0)*F11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="16">
         <f>E11/D11</f>
-        <v>279.64205816554812</v>
+        <v>-56250</v>
       </c>
       <c r="J11" s="17">
         <f>E11*F11</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="13">
         <f>F11*D11</f>
-        <v>17.88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>483</v>
       </c>
       <c r="C12">
-        <v>20.86</v>
+        <v>0.67</v>
       </c>
       <c r="D12">
-        <v>21.85</v>
+        <v>-0.18</v>
       </c>
       <c r="E12" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F12" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F12" s="13">
         <v>0</v>
       </c>
       <c r="G12" s="13">
@@ -3215,7 +2990,7 @@
       </c>
       <c r="I12" s="16">
         <f>E12/D12</f>
-        <v>283.75286041189929</v>
+        <v>-25000</v>
       </c>
       <c r="J12" s="17">
         <f>E12*F12</f>
@@ -3226,23 +3001,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="16">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C13">
-        <v>21.6</v>
+        <v>0.8</v>
       </c>
       <c r="D13">
-        <v>21.68</v>
+        <v>-0.32</v>
       </c>
       <c r="E13" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F13" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F13" s="13">
         <v>0</v>
       </c>
       <c r="G13" s="13">
@@ -3255,7 +3030,7 @@
       </c>
       <c r="I13" s="16">
         <f>E13/D13</f>
-        <v>285.9778597785978</v>
+        <v>-14062.5</v>
       </c>
       <c r="J13" s="17">
         <f>E13*F13</f>
@@ -3266,23 +3041,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="16">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="C14">
-        <v>17.91</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>17.809999999999999</v>
+        <v>-0.32</v>
       </c>
       <c r="E14" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F14" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F14" s="13">
         <v>0</v>
       </c>
       <c r="G14" s="13">
@@ -3295,7 +3070,7 @@
       </c>
       <c r="I14" s="16">
         <f>E14/D14</f>
-        <v>286.35597978663674</v>
+        <v>-14062.5</v>
       </c>
       <c r="J14" s="17">
         <f>E14*F14</f>
@@ -3306,23 +3081,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C15">
-        <v>33.85</v>
+        <v>0.51</v>
       </c>
       <c r="D15">
-        <v>29.88</v>
+        <v>-0.33</v>
       </c>
       <c r="E15" s="3">
-        <v>8600</v>
-      </c>
-      <c r="F15" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F15" s="13">
         <v>0</v>
       </c>
       <c r="G15" s="13">
@@ -3335,7 +3110,7 @@
       </c>
       <c r="I15" s="16">
         <f>E15/D15</f>
-        <v>287.81793842034807</v>
+        <v>-13636.363636363636</v>
       </c>
       <c r="J15" s="17">
         <f>E15*F15</f>
@@ -3346,23 +3121,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>408</v>
+        <v>493</v>
       </c>
       <c r="C16">
-        <v>27.59</v>
+        <v>2.58</v>
       </c>
       <c r="D16">
-        <v>25.61</v>
+        <v>-0.46</v>
       </c>
       <c r="E16" s="3">
-        <v>7400</v>
-      </c>
-      <c r="F16" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F16" s="13">
         <v>0</v>
       </c>
       <c r="G16" s="13">
@@ -3375,7 +3150,7 @@
       </c>
       <c r="I16" s="16">
         <f>E16/D16</f>
-        <v>288.94962905115187</v>
+        <v>-9782.608695652174</v>
       </c>
       <c r="J16" s="17">
         <f>E16*F16</f>
@@ -3386,23 +3161,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>425</v>
+        <v>503</v>
       </c>
       <c r="C17">
-        <v>19.04</v>
+        <v>0.6</v>
       </c>
       <c r="D17">
-        <v>19.72</v>
+        <v>-1.01</v>
       </c>
       <c r="E17" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F17" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="13">
         <v>0</v>
       </c>
       <c r="G17" s="13">
@@ -3415,7 +3190,7 @@
       </c>
       <c r="I17" s="16">
         <f>E17/D17</f>
-        <v>289.04665314401626</v>
+        <v>-4455.4455445544554</v>
       </c>
       <c r="J17" s="17">
         <f>E17*F17</f>
@@ -3426,23 +3201,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>263</v>
+        <v>495</v>
       </c>
       <c r="C18">
-        <v>20.18</v>
+        <v>0.8</v>
       </c>
       <c r="D18">
-        <v>19.02</v>
+        <v>-1.89</v>
       </c>
       <c r="E18" s="3">
-        <v>5500</v>
-      </c>
-      <c r="F18" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F18" s="13">
         <v>0</v>
       </c>
       <c r="G18" s="13">
@@ -3455,7 +3230,7 @@
       </c>
       <c r="I18" s="16">
         <f>E18/D18</f>
-        <v>289.16929547844376</v>
+        <v>-2380.9523809523812</v>
       </c>
       <c r="J18" s="17">
         <f>E18*F18</f>
@@ -3466,23 +3241,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C19">
-        <v>20.49</v>
+        <v>-0.25</v>
       </c>
       <c r="D19">
-        <v>20.399999999999999</v>
+        <v>-2.19</v>
       </c>
       <c r="E19" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F19" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F19" s="13">
         <v>0</v>
       </c>
       <c r="G19" s="13">
@@ -3495,7 +3270,7 @@
       </c>
       <c r="I19" s="16">
         <f>E19/D19</f>
-        <v>289.21568627450984</v>
+        <v>-2054.7945205479455</v>
       </c>
       <c r="J19" s="17">
         <f>E19*F19</f>
@@ -3506,23 +3281,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="C20">
-        <v>17.809999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="D20">
-        <v>18.25</v>
+        <v>-2.38</v>
       </c>
       <c r="E20" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F20" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F20" s="13">
         <v>0</v>
       </c>
       <c r="G20" s="13">
@@ -3535,7 +3310,7 @@
       </c>
       <c r="I20" s="16">
         <f>E20/D20</f>
-        <v>290.41095890410958</v>
+        <v>-1890.7563025210086</v>
       </c>
       <c r="J20" s="17">
         <f>E20*F20</f>
@@ -3546,23 +3321,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>474</v>
+        <v>406</v>
       </c>
       <c r="C21">
-        <v>27.47</v>
+        <v>27.59</v>
       </c>
       <c r="D21">
-        <v>24.76</v>
+        <v>26.52</v>
       </c>
       <c r="E21" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F21" s="15">
+        <v>7400</v>
+      </c>
+      <c r="F21" s="13">
         <v>0</v>
       </c>
       <c r="G21" s="13">
@@ -3575,7 +3350,7 @@
       </c>
       <c r="I21" s="16">
         <f>E21/D21</f>
-        <v>290.79159935379641</v>
+        <v>279.03469079939669</v>
       </c>
       <c r="J21" s="17">
         <f>E21*F21</f>
@@ -3586,23 +3361,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="C22">
-        <v>26.18</v>
+        <v>20.86</v>
       </c>
       <c r="D22">
-        <v>24.4</v>
+        <v>22</v>
       </c>
       <c r="E22" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F22" s="15">
+        <v>6200</v>
+      </c>
+      <c r="F22" s="13">
         <v>0</v>
       </c>
       <c r="G22" s="13">
@@ -3615,7 +3390,7 @@
       </c>
       <c r="I22" s="16">
         <f>E22/D22</f>
-        <v>290.98360655737707</v>
+        <v>281.81818181818181</v>
       </c>
       <c r="J22" s="17">
         <f>E22*F22</f>
@@ -3626,23 +3401,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="C23">
-        <v>21.67</v>
+        <v>23.54</v>
       </c>
       <c r="D23">
-        <v>18.21</v>
+        <v>22.01</v>
       </c>
       <c r="E23" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F23" s="15">
+        <v>6300</v>
+      </c>
+      <c r="F23" s="13">
         <v>0</v>
       </c>
       <c r="G23" s="13">
@@ -3655,7 +3430,7 @@
       </c>
       <c r="I23" s="16">
         <f>E23/D23</f>
-        <v>291.04887424492034</v>
+        <v>286.23353021353927</v>
       </c>
       <c r="J23" s="17">
         <f>E23*F23</f>
@@ -3666,23 +3441,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>238</v>
+        <v>405</v>
       </c>
       <c r="C24">
-        <v>23.54</v>
+        <v>31.6</v>
       </c>
       <c r="D24">
-        <v>21.61</v>
+        <v>28.59</v>
       </c>
       <c r="E24" s="3">
-        <v>6300</v>
-      </c>
-      <c r="F24" s="15">
+        <v>8200</v>
+      </c>
+      <c r="F24" s="13">
         <v>0</v>
       </c>
       <c r="G24" s="13">
@@ -3695,7 +3470,7 @@
       </c>
       <c r="I24" s="16">
         <f>E24/D24</f>
-        <v>291.53169828782973</v>
+        <v>286.81357117873381</v>
       </c>
       <c r="J24" s="17">
         <f>E24*F24</f>
@@ -3706,24 +3481,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16">
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C25">
-        <v>31.6</v>
+        <v>32.840000000000003</v>
       </c>
       <c r="D25">
-        <v>28.04</v>
+        <v>28.65</v>
       </c>
       <c r="E25" s="3">
-        <v>8200</v>
-      </c>
-      <c r="F25" s="15">
-        <v>1</v>
+        <v>8300</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
       </c>
       <c r="G25" s="13">
         <f>IF(A25="G",1,0)*F25</f>
@@ -3731,38 +3506,38 @@
       </c>
       <c r="H25" s="13">
         <f>IF(A25="F",1,0)*F25</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="16">
         <f>E25/D25</f>
-        <v>292.43937232524968</v>
+        <v>289.70331588132638</v>
       </c>
       <c r="J25" s="17">
         <f>E25*F25</f>
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="K25" s="13">
         <f>F25*D25</f>
-        <v>28.04</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C26">
-        <v>22.01</v>
+        <v>25.23</v>
       </c>
       <c r="D26">
-        <v>21.18</v>
+        <v>24.74</v>
       </c>
       <c r="E26" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F26" s="15">
+        <v>7200</v>
+      </c>
+      <c r="F26" s="13">
         <v>0</v>
       </c>
       <c r="G26" s="13">
@@ -3775,7 +3550,7 @@
       </c>
       <c r="I26" s="16">
         <f>E26/D26</f>
-        <v>292.72898961284233</v>
+        <v>291.02667744543254</v>
       </c>
       <c r="J26" s="17">
         <f>E26*F26</f>
@@ -3786,23 +3561,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="16">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="C27">
-        <v>32.840000000000003</v>
+        <v>25.79</v>
       </c>
       <c r="D27">
-        <v>28.33</v>
+        <v>23.95</v>
       </c>
       <c r="E27" s="3">
-        <v>8300</v>
-      </c>
-      <c r="F27" s="15">
+        <v>7100</v>
+      </c>
+      <c r="F27" s="13">
         <v>0</v>
       </c>
       <c r="G27" s="13">
@@ -3815,7 +3590,7 @@
       </c>
       <c r="I27" s="16">
         <f>E27/D27</f>
-        <v>292.97564419343456</v>
+        <v>296.45093945720254</v>
       </c>
       <c r="J27" s="17">
         <f>E27*F27</f>
@@ -3826,23 +3601,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="C28">
-        <v>18.12</v>
+        <v>27.66</v>
       </c>
       <c r="D28">
-        <v>18.670000000000002</v>
+        <v>24.21</v>
       </c>
       <c r="E28" s="3">
-        <v>5500</v>
-      </c>
-      <c r="F28" s="15">
+        <v>7200</v>
+      </c>
+      <c r="F28" s="13">
         <v>0</v>
       </c>
       <c r="G28" s="13">
@@ -3855,7 +3630,7 @@
       </c>
       <c r="I28" s="16">
         <f>E28/D28</f>
-        <v>294.59025174076055</v>
+        <v>297.3977695167286</v>
       </c>
       <c r="J28" s="17">
         <f>E28*F28</f>
@@ -3866,23 +3641,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>479</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>22.14</v>
+        <v>27.56</v>
       </c>
       <c r="D29">
-        <v>23.72</v>
+        <v>27.15</v>
       </c>
       <c r="E29" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F29" s="15">
+        <v>8100</v>
+      </c>
+      <c r="F29" s="13">
         <v>0</v>
       </c>
       <c r="G29" s="13">
@@ -3895,7 +3670,7 @@
       </c>
       <c r="I29" s="16">
         <f>E29/D29</f>
-        <v>295.10961214165263</v>
+        <v>298.3425414364641</v>
       </c>
       <c r="J29" s="17">
         <f>E29*F29</f>
@@ -3906,23 +3681,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="16">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>418</v>
       </c>
       <c r="C30">
-        <v>27.56</v>
+        <v>18.12</v>
       </c>
       <c r="D30">
-        <v>27.4</v>
+        <v>18.04</v>
       </c>
       <c r="E30" s="3">
-        <v>8100</v>
-      </c>
-      <c r="F30" s="15">
+        <v>5500</v>
+      </c>
+      <c r="F30" s="13">
         <v>0</v>
       </c>
       <c r="G30" s="13">
@@ -3935,7 +3710,7 @@
       </c>
       <c r="I30" s="16">
         <f>E30/D30</f>
-        <v>295.6204379562044</v>
+        <v>304.8780487804878</v>
       </c>
       <c r="J30" s="17">
         <f>E30*F30</f>
@@ -3946,23 +3721,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C31">
-        <v>25.23</v>
+        <v>26.8</v>
       </c>
       <c r="D31">
-        <v>24.3</v>
+        <v>24.89</v>
       </c>
       <c r="E31" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F31" s="15">
+        <v>7700</v>
+      </c>
+      <c r="F31" s="13">
         <v>0</v>
       </c>
       <c r="G31" s="13">
@@ -3975,7 +3750,7 @@
       </c>
       <c r="I31" s="16">
         <f>E31/D31</f>
-        <v>296.2962962962963</v>
+        <v>309.36118923262353</v>
       </c>
       <c r="J31" s="17">
         <f>E31*F31</f>
@@ -3986,23 +3761,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C32">
-        <v>14.36</v>
+        <v>23.46</v>
       </c>
       <c r="D32">
-        <v>15.13</v>
+        <v>22.56</v>
       </c>
       <c r="E32" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F32" s="15">
+        <v>7000</v>
+      </c>
+      <c r="F32" s="13">
         <v>0</v>
       </c>
       <c r="G32" s="13">
@@ -4015,7 +3790,7 @@
       </c>
       <c r="I32" s="16">
         <f>E32/D32</f>
-        <v>297.42233972240581</v>
+        <v>310.28368794326241</v>
       </c>
       <c r="J32" s="17">
         <f>E32*F32</f>
@@ -4026,23 +3801,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>503</v>
+        <v>289</v>
       </c>
       <c r="C33">
-        <v>18.57</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="D33">
-        <v>18.75</v>
+        <v>18.8</v>
       </c>
       <c r="E33" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F33" s="15">
+        <v>5900</v>
+      </c>
+      <c r="F33" s="13">
         <v>0</v>
       </c>
       <c r="G33" s="13">
@@ -4055,7 +3830,7 @@
       </c>
       <c r="I33" s="16">
         <f>E33/D33</f>
-        <v>298.66666666666669</v>
+        <v>313.82978723404256</v>
       </c>
       <c r="J33" s="17">
         <f>E33*F33</f>
@@ -4066,23 +3841,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>411</v>
       </c>
       <c r="C34">
-        <v>18.03</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="D34">
-        <v>18.05</v>
+        <v>18.45</v>
       </c>
       <c r="E34" s="3">
-        <v>5400</v>
-      </c>
-      <c r="F34" s="15">
+        <v>5800</v>
+      </c>
+      <c r="F34" s="13">
         <v>0</v>
       </c>
       <c r="G34" s="13">
@@ -4095,7 +3870,7 @@
       </c>
       <c r="I34" s="16">
         <f>E34/D34</f>
-        <v>299.16897506925204</v>
+        <v>314.36314363143634</v>
       </c>
       <c r="J34" s="17">
         <f>E34*F34</f>
@@ -4106,23 +3881,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16">
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>544</v>
+        <v>444</v>
       </c>
       <c r="C35">
-        <v>14.18</v>
+        <v>22.48</v>
       </c>
       <c r="D35">
-        <v>15.02</v>
+        <v>20.63</v>
       </c>
       <c r="E35" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F35" s="15">
+        <v>6500</v>
+      </c>
+      <c r="F35" s="13">
         <v>0</v>
       </c>
       <c r="G35" s="13">
@@ -4135,7 +3910,7 @@
       </c>
       <c r="I35" s="16">
         <f>E35/D35</f>
-        <v>299.6005326231691</v>
+        <v>315.07513330101796</v>
       </c>
       <c r="J35" s="17">
         <f>E35*F35</f>
@@ -4146,23 +3921,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16">
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="C36">
-        <v>27.66</v>
+        <v>21.39</v>
       </c>
       <c r="D36">
-        <v>23.8</v>
+        <v>19.61</v>
       </c>
       <c r="E36" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F36" s="15">
+        <v>6200</v>
+      </c>
+      <c r="F36" s="13">
         <v>0</v>
       </c>
       <c r="G36" s="13">
@@ -4175,7 +3950,7 @@
       </c>
       <c r="I36" s="16">
         <f>E36/D36</f>
-        <v>302.52100840336135</v>
+        <v>316.16522182559919</v>
       </c>
       <c r="J36" s="17">
         <f>E36*F36</f>
@@ -4186,23 +3961,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16">
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="C37">
-        <v>17.89</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="D37">
-        <v>16.8</v>
+        <v>15.42</v>
       </c>
       <c r="E37" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F37" s="15">
+        <v>4900</v>
+      </c>
+      <c r="F37" s="13">
         <v>0</v>
       </c>
       <c r="G37" s="13">
@@ -4215,7 +3990,7 @@
       </c>
       <c r="I37" s="16">
         <f>E37/D37</f>
-        <v>303.57142857142856</v>
+        <v>317.76913099870296</v>
       </c>
       <c r="J37" s="17">
         <f>E37*F37</f>
@@ -4226,23 +4001,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16">
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="C38">
-        <v>19.260000000000002</v>
+        <v>18.43</v>
       </c>
       <c r="D38">
-        <v>19.079999999999998</v>
+        <v>15.95</v>
       </c>
       <c r="E38" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F38" s="15">
+        <v>5100</v>
+      </c>
+      <c r="F38" s="13">
         <v>0</v>
       </c>
       <c r="G38" s="13">
@@ -4255,7 +4030,7 @@
       </c>
       <c r="I38" s="16">
         <f>E38/D38</f>
-        <v>303.9832285115304</v>
+        <v>319.74921630094047</v>
       </c>
       <c r="J38" s="17">
         <f>E38*F38</f>
@@ -4266,23 +4041,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>510</v>
+        <v>402</v>
       </c>
       <c r="C39">
-        <v>15.92</v>
+        <v>28.51</v>
       </c>
       <c r="D39">
-        <v>16.73</v>
+        <v>26.22</v>
       </c>
       <c r="E39" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F39" s="15">
+        <v>8400</v>
+      </c>
+      <c r="F39" s="13">
         <v>0</v>
       </c>
       <c r="G39" s="13">
@@ -4295,7 +4070,7 @@
       </c>
       <c r="I39" s="16">
         <f>E39/D39</f>
-        <v>304.84160191273162</v>
+        <v>320.36613272311212</v>
       </c>
       <c r="J39" s="17">
         <f>E39*F39</f>
@@ -4306,23 +4081,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>478</v>
+        <v>410</v>
       </c>
       <c r="C40">
-        <v>25.79</v>
+        <v>25.32</v>
       </c>
       <c r="D40">
-        <v>23.25</v>
+        <v>20.93</v>
       </c>
       <c r="E40" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F40" s="15">
+        <v>6800</v>
+      </c>
+      <c r="F40" s="13">
         <v>0</v>
       </c>
       <c r="G40" s="13">
@@ -4335,7 +4110,7 @@
       </c>
       <c r="I40" s="16">
         <f>E40/D40</f>
-        <v>305.3763440860215</v>
+        <v>324.89249880554229</v>
       </c>
       <c r="J40" s="17">
         <f>E40*F40</f>
@@ -4346,23 +4121,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="16">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>449</v>
       </c>
       <c r="C41">
-        <v>24.31</v>
+        <v>18.73</v>
       </c>
       <c r="D41">
-        <v>23.51</v>
+        <v>17.23</v>
       </c>
       <c r="E41" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F41" s="15">
+        <v>5600</v>
+      </c>
+      <c r="F41" s="13">
         <v>0</v>
       </c>
       <c r="G41" s="13">
@@ -4375,7 +4150,7 @@
       </c>
       <c r="I41" s="16">
         <f>E41/D41</f>
-        <v>306.25265844321564</v>
+        <v>325.01450957632034</v>
       </c>
       <c r="J41" s="17">
         <f>E41*F41</f>
@@ -4386,23 +4161,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="16">
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>477</v>
+        <v>413</v>
       </c>
       <c r="C42">
-        <v>22.5</v>
+        <v>18.84</v>
       </c>
       <c r="D42">
-        <v>23.14</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="E42" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F42" s="15">
+        <v>5500</v>
+      </c>
+      <c r="F42" s="13">
         <v>0</v>
       </c>
       <c r="G42" s="13">
@@ -4415,7 +4190,7 @@
       </c>
       <c r="I42" s="16">
         <f>E42/D42</f>
-        <v>306.82800345721694</v>
+        <v>327.18619869125524</v>
       </c>
       <c r="J42" s="17">
         <f>E42*F42</f>
@@ -4426,23 +4201,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="16">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="C43">
-        <v>20.71</v>
+        <v>21.47</v>
       </c>
       <c r="D43">
-        <v>19.54</v>
+        <v>20.03</v>
       </c>
       <c r="E43" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F43" s="15">
+        <v>6600</v>
+      </c>
+      <c r="F43" s="13">
         <v>0</v>
       </c>
       <c r="G43" s="13">
@@ -4455,7 +4230,7 @@
       </c>
       <c r="I43" s="16">
         <f>E43/D43</f>
-        <v>307.06243602865919</v>
+        <v>329.50574138791808</v>
       </c>
       <c r="J43" s="17">
         <f>E43*F43</f>
@@ -4466,23 +4241,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="C44">
-        <v>12.27</v>
+        <v>20.37</v>
       </c>
       <c r="D44">
-        <v>14.64</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="E44" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F44" s="15">
+        <v>5800</v>
+      </c>
+      <c r="F44" s="13">
         <v>0</v>
       </c>
       <c r="G44" s="13">
@@ -4495,7 +4270,7 @@
       </c>
       <c r="I44" s="16">
         <f>E44/D44</f>
-        <v>307.37704918032784</v>
+        <v>330.29612756264237</v>
       </c>
       <c r="J44" s="17">
         <f>E44*F44</f>
@@ -4506,23 +4281,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="16">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C45">
-        <v>33.950000000000003</v>
+        <v>17.41</v>
       </c>
       <c r="D45">
-        <v>29.27</v>
+        <v>17.55</v>
       </c>
       <c r="E45" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F45" s="15">
+        <v>5800</v>
+      </c>
+      <c r="F45" s="13">
         <v>0</v>
       </c>
       <c r="G45" s="13">
@@ -4535,7 +4310,7 @@
       </c>
       <c r="I45" s="16">
         <f>E45/D45</f>
-        <v>307.48206354629315</v>
+        <v>330.48433048433048</v>
       </c>
       <c r="J45" s="17">
         <f>E45*F45</f>
@@ -4546,23 +4321,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="16">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="C46">
-        <v>16.71</v>
+        <v>26.61</v>
       </c>
       <c r="D46">
-        <v>16.25</v>
+        <v>22.88</v>
       </c>
       <c r="E46" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F46" s="15">
+        <v>7600</v>
+      </c>
+      <c r="F46" s="13">
         <v>0</v>
       </c>
       <c r="G46" s="13">
@@ -4575,7 +4350,7 @@
       </c>
       <c r="I46" s="16">
         <f>E46/D46</f>
-        <v>307.69230769230768</v>
+        <v>332.16783216783216</v>
       </c>
       <c r="J46" s="17">
         <f>E46*F46</f>
@@ -4586,23 +4361,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="16">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>512</v>
+        <v>51</v>
       </c>
       <c r="C47">
-        <v>16.5</v>
+        <v>15.21</v>
       </c>
       <c r="D47">
-        <v>16.5</v>
+        <v>15.42</v>
       </c>
       <c r="E47" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F47" s="15">
+        <v>5200</v>
+      </c>
+      <c r="F47" s="13">
         <v>0</v>
       </c>
       <c r="G47" s="13">
@@ -4615,7 +4390,7 @@
       </c>
       <c r="I47" s="16">
         <f>E47/D47</f>
-        <v>309.09090909090907</v>
+        <v>337.22438391699092</v>
       </c>
       <c r="J47" s="17">
         <f>E47*F47</f>
@@ -4626,23 +4401,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
       <c r="C48">
-        <v>18.86</v>
+        <v>16.43</v>
       </c>
       <c r="D48">
-        <v>17.84</v>
+        <v>17.170000000000002</v>
       </c>
       <c r="E48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F48" s="15">
+        <v>5800</v>
+      </c>
+      <c r="F48" s="13">
         <v>0</v>
       </c>
       <c r="G48" s="13">
@@ -4655,7 +4430,7 @@
       </c>
       <c r="I48" s="16">
         <f>E48/D48</f>
-        <v>313.9013452914798</v>
+        <v>337.79848573092602</v>
       </c>
       <c r="J48" s="17">
         <f>E48*F48</f>
@@ -4666,23 +4441,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16">
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>485</v>
+        <v>67</v>
       </c>
       <c r="C49">
-        <v>20.02</v>
+        <v>14.66</v>
       </c>
       <c r="D49">
-        <v>20.55</v>
+        <v>13.56</v>
       </c>
       <c r="E49" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F49" s="15">
+        <v>4600</v>
+      </c>
+      <c r="F49" s="13">
         <v>0</v>
       </c>
       <c r="G49" s="13">
@@ -4695,7 +4470,7 @@
       </c>
       <c r="I49" s="16">
         <f>E49/D49</f>
-        <v>316.30170316301701</v>
+        <v>339.23303834808257</v>
       </c>
       <c r="J49" s="17">
         <f>E49*F49</f>
@@ -4706,23 +4481,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="16">
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="C50">
-        <v>13.29</v>
+        <v>16.48</v>
       </c>
       <c r="D50">
-        <v>15.17</v>
+        <v>14.59</v>
       </c>
       <c r="E50" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F50" s="15">
+        <v>5100</v>
+      </c>
+      <c r="F50" s="13">
         <v>0</v>
       </c>
       <c r="G50" s="13">
@@ -4735,7 +4510,7 @@
       </c>
       <c r="I50" s="16">
         <f>E50/D50</f>
-        <v>316.41397495056032</v>
+        <v>349.55448937628512</v>
       </c>
       <c r="J50" s="17">
         <f>E50*F50</f>
@@ -4746,23 +4521,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="16">
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
       <c r="C51">
-        <v>18.84</v>
+        <v>13.33</v>
       </c>
       <c r="D51">
-        <v>17.32</v>
+        <v>13.04</v>
       </c>
       <c r="E51" s="3">
-        <v>5500</v>
-      </c>
-      <c r="F51" s="15">
+        <v>4600</v>
+      </c>
+      <c r="F51" s="13">
         <v>0</v>
       </c>
       <c r="G51" s="13">
@@ -4775,7 +4550,7 @@
       </c>
       <c r="I51" s="16">
         <f>E51/D51</f>
-        <v>317.55196304849886</v>
+        <v>352.76073619631904</v>
       </c>
       <c r="J51" s="17">
         <f>E51*F51</f>
@@ -4786,23 +4561,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="16">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>289</v>
+        <v>456</v>
       </c>
       <c r="C52">
-        <v>19.809999999999999</v>
+        <v>13.78</v>
       </c>
       <c r="D52">
-        <v>18.5</v>
+        <v>13.21</v>
       </c>
       <c r="E52" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F52" s="15">
+        <v>4700</v>
+      </c>
+      <c r="F52" s="13">
         <v>0</v>
       </c>
       <c r="G52" s="13">
@@ -4815,7 +4590,7 @@
       </c>
       <c r="I52" s="16">
         <f>E52/D52</f>
-        <v>318.91891891891891</v>
+        <v>355.79106737320211</v>
       </c>
       <c r="J52" s="17">
         <f>E52*F52</f>
@@ -4826,23 +4601,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="16">
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>486</v>
+        <v>441</v>
       </c>
       <c r="C53">
-        <v>22.48</v>
+        <v>21.54</v>
       </c>
       <c r="D53">
-        <v>20.329999999999998</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="E53" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F53" s="15">
+        <v>7000</v>
+      </c>
+      <c r="F53" s="13">
         <v>0</v>
       </c>
       <c r="G53" s="13">
@@ -4855,7 +4630,7 @@
       </c>
       <c r="I53" s="16">
         <f>E53/D53</f>
-        <v>319.72454500737831</v>
+        <v>360.08230452674894</v>
       </c>
       <c r="J53" s="17">
         <f>E53*F53</f>
@@ -4866,23 +4641,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="16">
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>504</v>
+        <v>381</v>
       </c>
       <c r="C54">
-        <v>20.149999999999999</v>
+        <v>14.51</v>
       </c>
       <c r="D54">
-        <v>16.559999999999999</v>
+        <v>12.96</v>
       </c>
       <c r="E54" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F54" s="15">
+        <v>4700</v>
+      </c>
+      <c r="F54" s="13">
         <v>0</v>
       </c>
       <c r="G54" s="13">
@@ -4895,7 +4670,7 @@
       </c>
       <c r="I54" s="16">
         <f>E54/D54</f>
-        <v>320.04830917874398</v>
+        <v>362.65432098765427</v>
       </c>
       <c r="J54" s="17">
         <f>E54*F54</f>
@@ -4906,23 +4681,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="16">
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="C55">
-        <v>24.14</v>
+        <v>10.86</v>
       </c>
       <c r="D55">
-        <v>20.3</v>
+        <v>12.31</v>
       </c>
       <c r="E55" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F55" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F55" s="13">
         <v>0</v>
       </c>
       <c r="G55" s="13">
@@ -4935,7 +4710,7 @@
       </c>
       <c r="I55" s="16">
         <f>E55/D55</f>
-        <v>320.19704433497537</v>
+        <v>365.55645816409424</v>
       </c>
       <c r="J55" s="17">
         <f>E55*F55</f>
@@ -4946,23 +4721,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="16">
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>508</v>
+        <v>63</v>
       </c>
       <c r="C56">
-        <v>18.43</v>
+        <v>13.84</v>
       </c>
       <c r="D56">
-        <v>15.89</v>
+        <v>12.55</v>
       </c>
       <c r="E56" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F56" s="15">
+        <v>4600</v>
+      </c>
+      <c r="F56" s="13">
         <v>0</v>
       </c>
       <c r="G56" s="13">
@@ -4975,7 +4750,7 @@
       </c>
       <c r="I56" s="16">
         <f>E56/D56</f>
-        <v>320.95657646318438</v>
+        <v>366.53386454183266</v>
       </c>
       <c r="J56" s="17">
         <f>E56*F56</f>
@@ -4986,23 +4761,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="16">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C57">
-        <v>26.8</v>
+        <v>13.85</v>
       </c>
       <c r="D57">
-        <v>23.99</v>
+        <v>13.88</v>
       </c>
       <c r="E57" s="3">
-        <v>7700</v>
-      </c>
-      <c r="F57" s="15">
+        <v>5100</v>
+      </c>
+      <c r="F57" s="13">
         <v>0</v>
       </c>
       <c r="G57" s="13">
@@ -5015,7 +4790,7 @@
       </c>
       <c r="I57" s="16">
         <f>E57/D57</f>
-        <v>320.96706961233849</v>
+        <v>367.43515850144092</v>
       </c>
       <c r="J57" s="17">
         <f>E57*F57</f>
@@ -5026,23 +4801,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="16">
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="C58">
-        <v>20.61</v>
+        <v>13.23</v>
       </c>
       <c r="D58">
-        <v>19.93</v>
+        <v>12.08</v>
       </c>
       <c r="E58" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F58" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F58" s="13">
         <v>0</v>
       </c>
       <c r="G58" s="13">
@@ -5055,7 +4830,7 @@
       </c>
       <c r="I58" s="16">
         <f>E58/D58</f>
-        <v>321.12393376818869</v>
+        <v>372.51655629139071</v>
       </c>
       <c r="J58" s="17">
         <f>E58*F58</f>
@@ -5066,23 +4841,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="16">
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>524</v>
+        <v>421</v>
       </c>
       <c r="C59">
-        <v>11.64</v>
+        <v>16.11</v>
       </c>
       <c r="D59">
-        <v>13.99</v>
+        <v>13.94</v>
       </c>
       <c r="E59" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F59" s="15">
+        <v>5200</v>
+      </c>
+      <c r="F59" s="13">
         <v>0</v>
       </c>
       <c r="G59" s="13">
@@ -5095,7 +4870,7 @@
       </c>
       <c r="I59" s="16">
         <f>E59/D59</f>
-        <v>321.65832737669763</v>
+        <v>373.02725968436158</v>
       </c>
       <c r="J59" s="17">
         <f>E59*F59</f>
@@ -5106,23 +4881,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="16">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="C60">
-        <v>20.37</v>
+        <v>24.32</v>
       </c>
       <c r="D60">
-        <v>18</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E60" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F60" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F60" s="13">
         <v>0</v>
       </c>
       <c r="G60" s="13">
@@ -5135,7 +4910,7 @@
       </c>
       <c r="I60" s="16">
         <f>E60/D60</f>
-        <v>322.22222222222223</v>
+        <v>376.8844221105528</v>
       </c>
       <c r="J60" s="17">
         <f>E60*F60</f>
@@ -5146,23 +4921,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="16">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>405</v>
+        <v>470</v>
       </c>
       <c r="C61">
-        <v>26.61</v>
+        <v>13.14</v>
       </c>
       <c r="D61">
-        <v>23.58</v>
+        <v>11.8</v>
       </c>
       <c r="E61" s="3">
-        <v>7600</v>
-      </c>
-      <c r="F61" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F61" s="13">
         <v>0</v>
       </c>
       <c r="G61" s="13">
@@ -5175,7 +4950,7 @@
       </c>
       <c r="I61" s="16">
         <f>E61/D61</f>
-        <v>322.30703986429182</v>
+        <v>381.35593220338978</v>
       </c>
       <c r="J61" s="17">
         <f>E61*F61</f>
@@ -5186,23 +4961,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="16">
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="C62">
-        <v>15.76</v>
+        <v>12.74</v>
       </c>
       <c r="D62">
-        <v>16.41</v>
+        <v>11.77</v>
       </c>
       <c r="E62" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F62" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F62" s="13">
         <v>0</v>
       </c>
       <c r="G62" s="13">
@@ -5215,7 +4990,7 @@
       </c>
       <c r="I62" s="16">
         <f>E62/D62</f>
-        <v>322.97379646556976</v>
+        <v>382.32795242141037</v>
       </c>
       <c r="J62" s="17">
         <f>E62*F62</f>
@@ -5226,23 +5001,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="16">
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>549</v>
+        <v>414</v>
       </c>
       <c r="C63">
-        <v>11.38</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="D63">
-        <v>13.89</v>
+        <v>14.57</v>
       </c>
       <c r="E63" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F63" s="15">
+        <v>5700</v>
+      </c>
+      <c r="F63" s="13">
         <v>0</v>
       </c>
       <c r="G63" s="13">
@@ -5255,7 +5030,7 @@
       </c>
       <c r="I63" s="16">
         <f>E63/D63</f>
-        <v>323.97408207343409</v>
+        <v>391.21482498284144</v>
       </c>
       <c r="J63" s="17">
         <f>E63*F63</f>
@@ -5266,23 +5041,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="16">
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="C64">
-        <v>24.62</v>
+        <v>11.38</v>
       </c>
       <c r="D64">
-        <v>21.2</v>
+        <v>11.33</v>
       </c>
       <c r="E64" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F64" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F64" s="13">
         <v>0</v>
       </c>
       <c r="G64" s="13">
@@ -5295,7 +5070,7 @@
       </c>
       <c r="I64" s="16">
         <f>E64/D64</f>
-        <v>325.47169811320754</v>
+        <v>397.17563989408649</v>
       </c>
       <c r="J64" s="17">
         <f>E64*F64</f>
@@ -5306,23 +5081,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="16">
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>490</v>
+        <v>324</v>
       </c>
       <c r="C65">
-        <v>21.39</v>
+        <v>12.01</v>
       </c>
       <c r="D65">
-        <v>19</v>
+        <v>11.88</v>
       </c>
       <c r="E65" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F65" s="15">
+        <v>4800</v>
+      </c>
+      <c r="F65" s="13">
         <v>0</v>
       </c>
       <c r="G65" s="13">
@@ -5335,7 +5110,7 @@
       </c>
       <c r="I65" s="16">
         <f>E65/D65</f>
-        <v>326.31578947368422</v>
+        <v>404.04040404040404</v>
       </c>
       <c r="J65" s="17">
         <f>E65*F65</f>
@@ -5346,23 +5121,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="16">
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
         <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>466</v>
       </c>
       <c r="C66">
-        <v>15.21</v>
+        <v>10.44</v>
       </c>
       <c r="D66">
-        <v>15.92</v>
+        <v>10.79</v>
       </c>
       <c r="E66" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F66" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F66" s="13">
         <v>0</v>
       </c>
       <c r="G66" s="13">
@@ -5375,7 +5150,7 @@
       </c>
       <c r="I66" s="16">
         <f>E66/D66</f>
-        <v>326.63316582914575</v>
+        <v>417.05282669138091</v>
       </c>
       <c r="J66" s="17">
         <f>E66*F66</f>
@@ -5386,23 +5161,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="16">
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="C67">
-        <v>28.51</v>
+        <v>10.73</v>
       </c>
       <c r="D67">
-        <v>25.68</v>
+        <v>10.78</v>
       </c>
       <c r="E67" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F67" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F67" s="13">
         <v>0</v>
       </c>
       <c r="G67" s="13">
@@ -5415,7 +5190,7 @@
       </c>
       <c r="I67" s="16">
         <f>E67/D67</f>
-        <v>327.10280373831779</v>
+        <v>417.43970315398889</v>
       </c>
       <c r="J67" s="17">
         <f>E67*F67</f>
@@ -5426,23 +5201,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="16">
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>519</v>
+        <v>420</v>
       </c>
       <c r="C68">
-        <v>13.4</v>
+        <v>13.67</v>
       </c>
       <c r="D68">
-        <v>14.63</v>
+        <v>10.48</v>
       </c>
       <c r="E68" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F68" s="15">
+        <v>4600</v>
+      </c>
+      <c r="F68" s="13">
         <v>0</v>
       </c>
       <c r="G68" s="13">
@@ -5455,7 +5230,7 @@
       </c>
       <c r="I68" s="16">
         <f>E68/D68</f>
-        <v>328.09295967190701</v>
+        <v>438.93129770992363</v>
       </c>
       <c r="J68" s="17">
         <f>E68*F68</f>
@@ -5466,23 +5241,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="16">
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>576</v>
+        <v>463</v>
       </c>
       <c r="C69">
-        <v>14.54</v>
+        <v>10.6</v>
       </c>
       <c r="D69">
-        <v>13.71</v>
+        <v>10.11</v>
       </c>
       <c r="E69" s="3">
         <v>4500</v>
       </c>
-      <c r="F69" s="15">
+      <c r="F69" s="13">
         <v>0</v>
       </c>
       <c r="G69" s="13">
@@ -5495,7 +5270,7 @@
       </c>
       <c r="I69" s="16">
         <f>E69/D69</f>
-        <v>328.22757111597372</v>
+        <v>445.10385756676561</v>
       </c>
       <c r="J69" s="17">
         <f>E69*F69</f>
@@ -5506,23 +5281,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="16">
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>482</v>
+        <v>321</v>
       </c>
       <c r="C70">
-        <v>23.46</v>
+        <v>12.35</v>
       </c>
       <c r="D70">
-        <v>21.28</v>
+        <v>10.96</v>
       </c>
       <c r="E70" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F70" s="15">
+        <v>4900</v>
+      </c>
+      <c r="F70" s="13">
         <v>0</v>
       </c>
       <c r="G70" s="13">
@@ -5535,7 +5310,7 @@
       </c>
       <c r="I70" s="16">
         <f>E70/D70</f>
-        <v>328.9473684210526</v>
+        <v>447.08029197080288</v>
       </c>
       <c r="J70" s="17">
         <f>E70*F70</f>
@@ -5546,23 +5321,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="16">
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="C71">
-        <v>24.04</v>
+        <v>10.039999999999999</v>
       </c>
       <c r="D71">
-        <v>18.54</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="E71" s="3">
-        <v>6100</v>
-      </c>
-      <c r="F71" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F71" s="13">
         <v>0</v>
       </c>
       <c r="G71" s="13">
@@ -5575,7 +5350,7 @@
       </c>
       <c r="I71" s="16">
         <f>E71/D71</f>
-        <v>329.01833872707658</v>
+        <v>471.20418848167537</v>
       </c>
       <c r="J71" s="17">
         <f>E71*F71</f>
@@ -5586,23 +5361,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="16">
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>461</v>
       </c>
       <c r="C72">
-        <v>14.66</v>
+        <v>9.09</v>
       </c>
       <c r="D72">
-        <v>13.95</v>
+        <v>9.42</v>
       </c>
       <c r="E72" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F72" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F72" s="13">
         <v>0</v>
       </c>
       <c r="G72" s="13">
@@ -5615,7 +5390,7 @@
       </c>
       <c r="I72" s="16">
         <f>E72/D72</f>
-        <v>329.74910394265237</v>
+        <v>477.70700636942678</v>
       </c>
       <c r="J72" s="17">
         <f>E72*F72</f>
@@ -5626,23 +5401,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="16">
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>470</v>
+        <v>68</v>
       </c>
       <c r="C73">
-        <v>34.700000000000003</v>
+        <v>8.1</v>
       </c>
       <c r="D73">
-        <v>28.2</v>
+        <v>9</v>
       </c>
       <c r="E73" s="3">
-        <v>9300</v>
-      </c>
-      <c r="F73" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F73" s="13">
         <v>0</v>
       </c>
       <c r="G73" s="13">
@@ -5655,7 +5430,7 @@
       </c>
       <c r="I73" s="16">
         <f>E73/D73</f>
-        <v>329.78723404255322</v>
+        <v>500</v>
       </c>
       <c r="J73" s="17">
         <f>E73*F73</f>
@@ -5666,23 +5441,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="16">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C74">
-        <v>22.53</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="D74">
-        <v>21.2</v>
+        <v>8.31</v>
       </c>
       <c r="E74" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F74" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F74" s="13">
         <v>0</v>
       </c>
       <c r="G74" s="13">
@@ -5695,7 +5470,7 @@
       </c>
       <c r="I74" s="16">
         <f>E74/D74</f>
-        <v>330.18867924528303</v>
+        <v>541.51624548736459</v>
       </c>
       <c r="J74" s="17">
         <f>E74*F74</f>
@@ -5706,23 +5481,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="16">
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>515</v>
+        <v>474</v>
       </c>
       <c r="C75">
-        <v>16.760000000000002</v>
+        <v>7.92</v>
       </c>
       <c r="D75">
-        <v>14.71</v>
+        <v>7.09</v>
       </c>
       <c r="E75" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F75" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F75" s="13">
         <v>0</v>
       </c>
       <c r="G75" s="13">
@@ -5735,7 +5510,7 @@
       </c>
       <c r="I75" s="16">
         <f>E75/D75</f>
-        <v>333.10673011556764</v>
+        <v>634.69675599435823</v>
       </c>
       <c r="J75" s="17">
         <f>E75*F75</f>
@@ -5746,23 +5521,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="16">
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>507</v>
+        <v>96</v>
       </c>
       <c r="C76">
-        <v>14.22</v>
+        <v>6.95</v>
       </c>
       <c r="D76">
-        <v>15.45</v>
+        <v>6.57</v>
       </c>
       <c r="E76" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F76" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F76" s="13">
         <v>0</v>
       </c>
       <c r="G76" s="13">
@@ -5775,7 +5550,7 @@
       </c>
       <c r="I76" s="16">
         <f>E76/D76</f>
-        <v>336.56957928802592</v>
+        <v>684.93150684931504</v>
       </c>
       <c r="J76" s="17">
         <f>E76*F76</f>
@@ -5786,23 +5561,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="16">
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="C77">
-        <v>25.32</v>
+        <v>6.5</v>
       </c>
       <c r="D77">
-        <v>20.12</v>
+        <v>6.27</v>
       </c>
       <c r="E77" s="3">
-        <v>6800</v>
-      </c>
-      <c r="F77" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F77" s="13">
         <v>0</v>
       </c>
       <c r="G77" s="13">
@@ -5815,7 +5590,7 @@
       </c>
       <c r="I77" s="16">
         <f>E77/D77</f>
-        <v>337.97216699801191</v>
+        <v>717.7033492822967</v>
       </c>
       <c r="J77" s="17">
         <f>E77*F77</f>
@@ -5826,23 +5601,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="16">
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
         <v>3</v>
       </c>
       <c r="B78" t="s">
-        <v>568</v>
+        <v>468</v>
       </c>
       <c r="C78">
-        <v>14.18</v>
+        <v>7.29</v>
       </c>
       <c r="D78">
-        <v>13.24</v>
+        <v>6.15</v>
       </c>
       <c r="E78" s="3">
         <v>4500</v>
       </c>
-      <c r="F78" s="15">
+      <c r="F78" s="13">
         <v>0</v>
       </c>
       <c r="G78" s="13">
@@ -5855,7 +5630,7 @@
       </c>
       <c r="I78" s="16">
         <f>E78/D78</f>
-        <v>339.87915407854985</v>
+        <v>731.70731707317066</v>
       </c>
       <c r="J78" s="17">
         <f>E78*F78</f>
@@ -5866,23 +5641,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="16">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>498</v>
+        <v>455</v>
       </c>
       <c r="C79">
-        <v>18.73</v>
+        <v>6.84</v>
       </c>
       <c r="D79">
-        <v>16.36</v>
+        <v>6.42</v>
       </c>
       <c r="E79" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F79" s="15">
+        <v>4800</v>
+      </c>
+      <c r="F79" s="13">
         <v>0</v>
       </c>
       <c r="G79" s="13">
@@ -5895,7 +5670,7 @@
       </c>
       <c r="I79" s="16">
         <f>E79/D79</f>
-        <v>342.29828850855745</v>
+        <v>747.6635514018692</v>
       </c>
       <c r="J79" s="17">
         <f>E79*F79</f>
@@ -5906,23 +5681,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="16">
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B80" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="C80">
-        <v>21.47</v>
+        <v>6.8</v>
       </c>
       <c r="D80">
-        <v>19.23</v>
+        <v>5.83</v>
       </c>
       <c r="E80" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F80" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F80" s="13">
         <v>0</v>
       </c>
       <c r="G80" s="13">
@@ -5935,7 +5710,7 @@
       </c>
       <c r="I80" s="16">
         <f>E80/D80</f>
-        <v>343.21372854914193</v>
+        <v>771.86963979416805</v>
       </c>
       <c r="J80" s="17">
         <f>E80*F80</f>
@@ -5946,23 +5721,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="16">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B81" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="C81">
-        <v>16.43</v>
+        <v>7.4</v>
       </c>
       <c r="D81">
-        <v>16.79</v>
+        <v>5.77</v>
       </c>
       <c r="E81" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F81" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F81" s="13">
         <v>0</v>
       </c>
       <c r="G81" s="13">
@@ -5975,7 +5750,7 @@
       </c>
       <c r="I81" s="16">
         <f>E81/D81</f>
-        <v>345.44371649791543</v>
+        <v>779.89601386481809</v>
       </c>
       <c r="J81" s="17">
         <f>E81*F81</f>
@@ -5986,23 +5761,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="16">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="C82">
-        <v>17.41</v>
+        <v>5.49</v>
       </c>
       <c r="D82">
-        <v>16.72</v>
+        <v>5.45</v>
       </c>
       <c r="E82" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F82" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F82" s="13">
         <v>0</v>
       </c>
       <c r="G82" s="13">
@@ -6015,7 +5790,7 @@
       </c>
       <c r="I82" s="16">
         <f>E82/D82</f>
-        <v>346.88995215311007</v>
+        <v>825.6880733944954</v>
       </c>
       <c r="J82" s="17">
         <f>E82*F82</f>
@@ -6026,23 +5801,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="16">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>3</v>
       </c>
       <c r="B83" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C83">
-        <v>23.87</v>
+        <v>6.29</v>
       </c>
       <c r="D83">
-        <v>20.68</v>
+        <v>5.43</v>
       </c>
       <c r="E83" s="3">
-        <v>7200</v>
-      </c>
-      <c r="F83" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F83" s="13">
         <v>0</v>
       </c>
       <c r="G83" s="13">
@@ -6055,7 +5830,7 @@
       </c>
       <c r="I83" s="16">
         <f>E83/D83</f>
-        <v>348.16247582205028</v>
+        <v>828.72928176795585</v>
       </c>
       <c r="J83" s="17">
         <f>E83*F83</f>
@@ -6066,23 +5841,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="16">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>3</v>
       </c>
       <c r="B84" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="C84">
-        <v>28.26</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="D84">
-        <v>24.02</v>
+        <v>5.36</v>
       </c>
       <c r="E84" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F84" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F84" s="13">
         <v>0</v>
       </c>
       <c r="G84" s="13">
@@ -6095,7 +5870,7 @@
       </c>
       <c r="I84" s="16">
         <f>E84/D84</f>
-        <v>349.70857618651127</v>
+        <v>839.55223880597009</v>
       </c>
       <c r="J84" s="17">
         <f>E84*F84</f>
@@ -6106,23 +5881,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="16">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C85">
-        <v>13.85</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="D85">
-        <v>14.55</v>
+        <v>5.23</v>
       </c>
       <c r="E85" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F85" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F85" s="13">
         <v>0</v>
       </c>
       <c r="G85" s="13">
@@ -6135,7 +5910,7 @@
       </c>
       <c r="I85" s="16">
         <f>E85/D85</f>
-        <v>350.51546391752578</v>
+        <v>860.42065009560224</v>
       </c>
       <c r="J85" s="17">
         <f>E85*F85</f>
@@ -6146,23 +5921,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="16">
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C86">
-        <v>23.41</v>
+        <v>5.74</v>
       </c>
       <c r="D86">
-        <v>19.43</v>
+        <v>4.95</v>
       </c>
       <c r="E86" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F86" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F86" s="13">
         <v>0</v>
       </c>
       <c r="G86" s="13">
@@ -6175,7 +5950,7 @@
       </c>
       <c r="I86" s="16">
         <f>E86/D86</f>
-        <v>355.12094698919196</v>
+        <v>909.09090909090901</v>
       </c>
       <c r="J86" s="17">
         <f>E86*F86</f>
@@ -6186,23 +5961,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="16">
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="C87">
-        <v>19.12</v>
+        <v>6.85</v>
       </c>
       <c r="D87">
-        <v>16.850000000000001</v>
+        <v>4.82</v>
       </c>
       <c r="E87" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F87" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F87" s="13">
         <v>0</v>
       </c>
       <c r="G87" s="13">
@@ -6215,7 +5990,7 @@
       </c>
       <c r="I87" s="16">
         <f>E87/D87</f>
-        <v>356.08308605341244</v>
+        <v>933.60995850622396</v>
       </c>
       <c r="J87" s="17">
         <f>E87*F87</f>
@@ -6226,23 +6001,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="16">
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>435</v>
       </c>
       <c r="C88">
-        <v>13.84</v>
+        <v>5.03</v>
       </c>
       <c r="D88">
-        <v>12.84</v>
+        <v>4.66</v>
       </c>
       <c r="E88" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F88" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F88" s="13">
         <v>0</v>
       </c>
       <c r="G88" s="13">
@@ -6255,7 +6030,7 @@
       </c>
       <c r="I88" s="16">
         <f>E88/D88</f>
-        <v>358.25545171339564</v>
+        <v>965.66523605150212</v>
       </c>
       <c r="J88" s="17">
         <f>E88*F88</f>
@@ -6266,23 +6041,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="16">
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B89" t="s">
-        <v>523</v>
+        <v>430</v>
       </c>
       <c r="C89">
-        <v>13.33</v>
+        <v>6.46</v>
       </c>
       <c r="D89">
-        <v>12.84</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E89" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F89" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F89" s="13">
         <v>0</v>
       </c>
       <c r="G89" s="13">
@@ -6295,7 +6070,7 @@
       </c>
       <c r="I89" s="16">
         <f>E89/D89</f>
-        <v>358.25545171339564</v>
+        <v>1034.4827586206898</v>
       </c>
       <c r="J89" s="17">
         <f>E89*F89</f>
@@ -6306,23 +6081,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="16">
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B90" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C90">
-        <v>21.54</v>
+        <v>5.67</v>
       </c>
       <c r="D90">
-        <v>19.34</v>
+        <v>4.25</v>
       </c>
       <c r="E90" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F90" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F90" s="13">
         <v>0</v>
       </c>
       <c r="G90" s="13">
@@ -6335,7 +6110,7 @@
       </c>
       <c r="I90" s="16">
         <f>E90/D90</f>
-        <v>361.94415718717681</v>
+        <v>1058.8235294117646</v>
       </c>
       <c r="J90" s="17">
         <f>E90*F90</f>
@@ -6346,23 +6121,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="16">
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
         <v>3</v>
       </c>
       <c r="B91" t="s">
-        <v>476</v>
+        <v>434</v>
       </c>
       <c r="C91">
-        <v>24.72</v>
+        <v>4.29</v>
       </c>
       <c r="D91">
-        <v>19.440000000000001</v>
+        <v>4.13</v>
       </c>
       <c r="E91" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F91" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F91" s="13">
         <v>0</v>
       </c>
       <c r="G91" s="13">
@@ -6375,7 +6150,7 @@
       </c>
       <c r="I91" s="16">
         <f>E91/D91</f>
-        <v>365.22633744855966</v>
+        <v>1089.588377723971</v>
       </c>
       <c r="J91" s="17">
         <f>E91*F91</f>
@@ -6386,23 +6161,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="16">
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B92" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="C92">
-        <v>12.98</v>
+        <v>3.89</v>
       </c>
       <c r="D92">
-        <v>12.59</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="E92" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F92" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F92" s="13">
         <v>0</v>
       </c>
       <c r="G92" s="13">
@@ -6415,7 +6190,7 @@
       </c>
       <c r="I92" s="16">
         <f>E92/D92</f>
-        <v>365.36934074662429</v>
+        <v>1108.3743842364534</v>
       </c>
       <c r="J92" s="17">
         <f>E92*F92</f>
@@ -6426,23 +6201,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="16">
+    <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B93" t="s">
-        <v>511</v>
+        <v>427</v>
       </c>
       <c r="C93">
-        <v>16.48</v>
+        <v>5.41</v>
       </c>
       <c r="D93">
-        <v>13.92</v>
+        <v>4.01</v>
       </c>
       <c r="E93" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F93" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F93" s="13">
         <v>0</v>
       </c>
       <c r="G93" s="13">
@@ -6455,7 +6230,7 @@
       </c>
       <c r="I93" s="16">
         <f>E93/D93</f>
-        <v>366.37931034482762</v>
+        <v>1122.1945137157109</v>
       </c>
       <c r="J93" s="17">
         <f>E93*F93</f>
@@ -6466,23 +6241,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="16">
+    <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>381</v>
+        <v>423</v>
       </c>
       <c r="C94">
-        <v>14.51</v>
+        <v>4.46</v>
       </c>
       <c r="D94">
-        <v>12.82</v>
+        <v>3.88</v>
       </c>
       <c r="E94" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F94" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F94" s="13">
         <v>0</v>
       </c>
       <c r="G94" s="13">
@@ -6495,7 +6270,7 @@
       </c>
       <c r="I94" s="16">
         <f>E94/D94</f>
-        <v>366.61466458658344</v>
+        <v>1159.7938144329896</v>
       </c>
       <c r="J94" s="17">
         <f>E94*F94</f>
@@ -6506,23 +6281,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="16">
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="C95">
-        <v>22.76</v>
+        <v>3.64</v>
       </c>
       <c r="D95">
-        <v>19.28</v>
+        <v>3.64</v>
       </c>
       <c r="E95" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F95" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F95" s="13">
         <v>0</v>
       </c>
       <c r="G95" s="13">
@@ -6535,7 +6310,7 @@
       </c>
       <c r="I95" s="16">
         <f>E95/D95</f>
-        <v>368.25726141078837</v>
+        <v>1236.2637362637363</v>
       </c>
       <c r="J95" s="17">
         <f>E95*F95</f>
@@ -6546,23 +6321,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="16">
+    <row r="96" spans="1:11">
       <c r="A96" t="s">
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>499</v>
+        <v>424</v>
       </c>
       <c r="C96">
-        <v>15.26</v>
+        <v>6.17</v>
       </c>
       <c r="D96">
-        <v>15.1</v>
+        <v>3.57</v>
       </c>
       <c r="E96" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F96" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F96" s="13">
         <v>0</v>
       </c>
       <c r="G96" s="13">
@@ -6575,7 +6350,7 @@
       </c>
       <c r="I96" s="16">
         <f>E96/D96</f>
-        <v>370.86092715231791</v>
+        <v>1260.5042016806724</v>
       </c>
       <c r="J96" s="17">
         <f>E96*F96</f>
@@ -6586,23 +6361,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="16">
+    <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C97">
-        <v>24.32</v>
+        <v>5.25</v>
       </c>
       <c r="D97">
-        <v>20.18</v>
+        <v>3.38</v>
       </c>
       <c r="E97" s="3">
-        <v>7500</v>
-      </c>
-      <c r="F97" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F97" s="13">
         <v>0</v>
       </c>
       <c r="G97" s="13">
@@ -6615,7 +6390,7 @@
       </c>
       <c r="I97" s="16">
         <f>E97/D97</f>
-        <v>371.65510406342912</v>
+        <v>1331.3609467455622</v>
       </c>
       <c r="J97" s="17">
         <f>E97*F97</f>
@@ -6626,23 +6401,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="16">
+    <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="C98">
-        <v>16.11</v>
+        <v>2.93</v>
       </c>
       <c r="D98">
-        <v>13.98</v>
+        <v>3.22</v>
       </c>
       <c r="E98" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F98" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F98" s="13">
         <v>0</v>
       </c>
       <c r="G98" s="13">
@@ -6655,7 +6430,7 @@
       </c>
       <c r="I98" s="16">
         <f>E98/D98</f>
-        <v>371.95994277539342</v>
+        <v>1397.5155279503106</v>
       </c>
       <c r="J98" s="17">
         <f>E98*F98</f>
@@ -6666,23 +6441,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="16">
+    <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>521</v>
+        <v>475</v>
       </c>
       <c r="C99">
-        <v>13.78</v>
+        <v>4.08</v>
       </c>
       <c r="D99">
-        <v>12.54</v>
+        <v>3.17</v>
       </c>
       <c r="E99" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F99" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F99" s="13">
         <v>0</v>
       </c>
       <c r="G99" s="13">
@@ -6695,7 +6470,7 @@
       </c>
       <c r="I99" s="16">
         <f>E99/D99</f>
-        <v>374.80063795853272</v>
+        <v>1419.5583596214512</v>
       </c>
       <c r="J99" s="17">
         <f>E99*F99</f>
@@ -6706,23 +6481,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="16">
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>535</v>
+        <v>436</v>
       </c>
       <c r="C100">
-        <v>10.86</v>
+        <v>6</v>
       </c>
       <c r="D100">
-        <v>11.96</v>
+        <v>3.14</v>
       </c>
       <c r="E100" s="3">
         <v>4500</v>
       </c>
-      <c r="F100" s="15">
+      <c r="F100" s="13">
         <v>0</v>
       </c>
       <c r="G100" s="13">
@@ -6735,7 +6510,7 @@
       </c>
       <c r="I100" s="16">
         <f>E100/D100</f>
-        <v>376.25418060200667</v>
+        <v>1433.1210191082803</v>
       </c>
       <c r="J100" s="17">
         <f>E100*F100</f>
@@ -6746,23 +6521,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="16">
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>424</v>
+        <v>131</v>
       </c>
       <c r="C101">
-        <v>16.829999999999998</v>
+        <v>3.54</v>
       </c>
       <c r="D101">
-        <v>15.06</v>
+        <v>2.93</v>
       </c>
       <c r="E101" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F101" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F101" s="13">
         <v>0</v>
       </c>
       <c r="G101" s="13">
@@ -6775,7 +6550,7 @@
       </c>
       <c r="I101" s="16">
         <f>E101/D101</f>
-        <v>378.48605577689244</v>
+        <v>1535.8361774744026</v>
       </c>
       <c r="J101" s="17">
         <f>E101*F101</f>
@@ -6786,23 +6561,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="16">
+    <row r="102" spans="1:11">
       <c r="A102" t="s">
         <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="C102">
-        <v>13.69</v>
+        <v>4.82</v>
       </c>
       <c r="D102">
-        <v>12.68</v>
+        <v>2.61</v>
       </c>
       <c r="E102" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F102" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F102" s="13">
         <v>0</v>
       </c>
       <c r="G102" s="13">
@@ -6815,7 +6590,7 @@
       </c>
       <c r="I102" s="16">
         <f>E102/D102</f>
-        <v>378.54889589905366</v>
+        <v>1724.1379310344828</v>
       </c>
       <c r="J102" s="17">
         <f>E102*F102</f>
@@ -6826,23 +6601,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="16">
+    <row r="103" spans="1:11">
       <c r="A103" t="s">
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>310</v>
+        <v>489</v>
       </c>
       <c r="C103">
-        <v>12.98</v>
+        <v>3.9</v>
       </c>
       <c r="D103">
-        <v>13.05</v>
+        <v>2.46</v>
       </c>
       <c r="E103" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F103" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F103" s="13">
         <v>0</v>
       </c>
       <c r="G103" s="13">
@@ -6855,7 +6630,7 @@
       </c>
       <c r="I103" s="16">
         <f>E103/D103</f>
-        <v>383.14176245210729</v>
+        <v>1829.2682926829268</v>
       </c>
       <c r="J103" s="17">
         <f>E103*F103</f>
@@ -6866,23 +6641,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="16">
+    <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C104">
-        <v>19.600000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="D104">
-        <v>15.87</v>
+        <v>2.13</v>
       </c>
       <c r="E104" s="3">
-        <v>6100</v>
-      </c>
-      <c r="F104" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F104" s="13">
         <v>0</v>
       </c>
       <c r="G104" s="13">
@@ -6895,7 +6670,7 @@
       </c>
       <c r="I104" s="16">
         <f>E104/D104</f>
-        <v>384.37303087586645</v>
+        <v>2112.6760563380285</v>
       </c>
       <c r="J104" s="17">
         <f>E104*F104</f>
@@ -6906,23 +6681,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="16">
+    <row r="105" spans="1:11">
       <c r="A105" t="s">
         <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>553</v>
+        <v>422</v>
       </c>
       <c r="C105">
-        <v>12.74</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D105">
-        <v>11.68</v>
+        <v>1.84</v>
       </c>
       <c r="E105" s="3">
         <v>4500</v>
       </c>
-      <c r="F105" s="15">
+      <c r="F105" s="13">
         <v>0</v>
       </c>
       <c r="G105" s="13">
@@ -6935,7 +6710,7 @@
       </c>
       <c r="I105" s="16">
         <f>E105/D105</f>
-        <v>385.27397260273972</v>
+        <v>2445.6521739130435</v>
       </c>
       <c r="J105" s="17">
         <f>E105*F105</f>
@@ -6946,23 +6721,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="16">
+    <row r="106" spans="1:11">
       <c r="A106" t="s">
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="C106">
-        <v>18.89</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>15.46</v>
+        <v>1.71</v>
       </c>
       <c r="E106" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F106" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F106" s="13">
         <v>0</v>
       </c>
       <c r="G106" s="13">
@@ -6975,7 +6750,7 @@
       </c>
       <c r="I106" s="16">
         <f>E106/D106</f>
-        <v>388.09831824062093</v>
+        <v>2631.5789473684213</v>
       </c>
       <c r="J106" s="17">
         <f>E106*F106</f>
@@ -6986,23 +6761,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="16">
+    <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B107" t="s">
-        <v>575</v>
+        <v>481</v>
       </c>
       <c r="C107">
-        <v>11.98</v>
+        <v>1.2</v>
       </c>
       <c r="D107">
-        <v>11.57</v>
+        <v>1.6</v>
       </c>
       <c r="E107" s="3">
         <v>4500</v>
       </c>
-      <c r="F107" s="15">
+      <c r="F107" s="13">
         <v>0</v>
       </c>
       <c r="G107" s="13">
@@ -7015,7 +6790,7 @@
       </c>
       <c r="I107" s="16">
         <f>E107/D107</f>
-        <v>388.93690579083835</v>
+        <v>2812.5</v>
       </c>
       <c r="J107" s="17">
         <f>E107*F107</f>
@@ -7026,23 +6801,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="16">
+    <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B108" t="s">
-        <v>561</v>
+        <v>88</v>
       </c>
       <c r="C108">
-        <v>13.23</v>
+        <v>1.59</v>
       </c>
       <c r="D108">
-        <v>11.52</v>
+        <v>1.32</v>
       </c>
       <c r="E108" s="3">
         <v>4500</v>
       </c>
-      <c r="F108" s="15">
+      <c r="F108" s="13">
         <v>0</v>
       </c>
       <c r="G108" s="13">
@@ -7055,7 +6830,7 @@
       </c>
       <c r="I108" s="16">
         <f>E108/D108</f>
-        <v>390.625</v>
+        <v>3409.090909090909</v>
       </c>
       <c r="J108" s="17">
         <f>E108*F108</f>
@@ -7066,23 +6841,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="16">
+    <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>560</v>
+        <v>487</v>
       </c>
       <c r="C109">
-        <v>13.14</v>
+        <v>1.73</v>
       </c>
       <c r="D109">
-        <v>11.47</v>
+        <v>1.19</v>
       </c>
       <c r="E109" s="3">
         <v>4500</v>
       </c>
-      <c r="F109" s="15">
+      <c r="F109" s="13">
         <v>0</v>
       </c>
       <c r="G109" s="13">
@@ -7095,7 +6870,7 @@
       </c>
       <c r="I109" s="16">
         <f>E109/D109</f>
-        <v>392.32781168265035</v>
+        <v>3781.5126050420172</v>
       </c>
       <c r="J109" s="17">
         <f>E109*F109</f>
@@ -7106,23 +6881,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="16">
+    <row r="110" spans="1:11">
       <c r="A110" t="s">
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C110">
-        <v>17.21</v>
+        <v>1.18</v>
       </c>
       <c r="D110">
-        <v>14.21</v>
+        <v>1.05</v>
       </c>
       <c r="E110" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F110" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F110" s="13">
         <v>0</v>
       </c>
       <c r="G110" s="13">
@@ -7135,7 +6910,7 @@
       </c>
       <c r="I110" s="16">
         <f>E110/D110</f>
-        <v>394.0886699507389</v>
+        <v>4285.7142857142853</v>
       </c>
       <c r="J110" s="17">
         <f>E110*F110</f>
@@ -7146,23 +6921,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="16">
+    <row r="111" spans="1:11">
       <c r="A111" t="s">
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>433</v>
+        <v>496</v>
       </c>
       <c r="C111">
-        <v>13.46</v>
+        <v>3.13</v>
       </c>
       <c r="D111">
-        <v>12.06</v>
+        <v>0.99</v>
       </c>
       <c r="E111" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F111" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F111" s="13">
         <v>0</v>
       </c>
       <c r="G111" s="13">
@@ -7175,7 +6950,7 @@
       </c>
       <c r="I111" s="16">
         <f>E111/D111</f>
-        <v>406.30182421227198</v>
+        <v>4545.454545454545</v>
       </c>
       <c r="J111" s="17">
         <f>E111*F111</f>
@@ -7186,23 +6961,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="16">
+    <row r="112" spans="1:11">
       <c r="A112" t="s">
         <v>3</v>
       </c>
       <c r="B112" t="s">
-        <v>324</v>
+        <v>502</v>
       </c>
       <c r="C112">
-        <v>12.01</v>
+        <v>0.95</v>
       </c>
       <c r="D112">
-        <v>11.7</v>
+        <v>0.75</v>
       </c>
       <c r="E112" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F112" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F112" s="13">
         <v>0</v>
       </c>
       <c r="G112" s="13">
@@ -7215,7 +6990,7 @@
       </c>
       <c r="I112" s="16">
         <f>E112/D112</f>
-        <v>410.25641025641028</v>
+        <v>6000</v>
       </c>
       <c r="J112" s="17">
         <f>E112*F112</f>
@@ -7226,23 +7001,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="16">
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
         <v>3</v>
       </c>
       <c r="B113" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C113">
-        <v>13.49</v>
+        <v>-1</v>
       </c>
       <c r="D113">
-        <v>12.88</v>
+        <v>0.59</v>
       </c>
       <c r="E113" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F113" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F113" s="13">
         <v>0</v>
       </c>
       <c r="G113" s="13">
@@ -7255,7 +7030,7 @@
       </c>
       <c r="I113" s="16">
         <f>E113/D113</f>
-        <v>411.49068322981361</v>
+        <v>7627.1186440677966</v>
       </c>
       <c r="J113" s="17">
         <f>E113*F113</f>
@@ -7266,23 +7041,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="16">
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="C114">
-        <v>11.38</v>
+        <v>0.88</v>
       </c>
       <c r="D114">
-        <v>10.92</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E114" s="3">
         <v>4500</v>
       </c>
-      <c r="F114" s="15">
+      <c r="F114" s="13">
         <v>0</v>
       </c>
       <c r="G114" s="13">
@@ -7295,7 +7070,7 @@
       </c>
       <c r="I114" s="16">
         <f>E114/D114</f>
-        <v>412.08791208791212</v>
+        <v>7894.7368421052643</v>
       </c>
       <c r="J114" s="17">
         <f>E114*F114</f>
@@ -7306,23 +7081,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="16">
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>551</v>
+        <v>497</v>
       </c>
       <c r="C115">
-        <v>10.44</v>
+        <v>0.88</v>
       </c>
       <c r="D115">
-        <v>10.92</v>
+        <v>0.54</v>
       </c>
       <c r="E115" s="3">
         <v>4500</v>
       </c>
-      <c r="F115" s="15">
+      <c r="F115" s="13">
         <v>0</v>
       </c>
       <c r="G115" s="13">
@@ -7335,7 +7110,7 @@
       </c>
       <c r="I115" s="16">
         <f>E115/D115</f>
-        <v>412.08791208791212</v>
+        <v>8333.3333333333321</v>
       </c>
       <c r="J115" s="17">
         <f>E115*F115</f>
@@ -7346,23 +7121,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="16">
+    <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="C116">
-        <v>12.4</v>
+        <v>1.24</v>
       </c>
       <c r="D116">
-        <v>10.77</v>
+        <v>0.27</v>
       </c>
       <c r="E116" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F116" s="15">
+        <v>3000</v>
+      </c>
+      <c r="F116" s="13">
         <v>0</v>
       </c>
       <c r="G116" s="13">
@@ -7375,7 +7150,7 @@
       </c>
       <c r="I116" s="16">
         <f>E116/D116</f>
-        <v>417.82729805013929</v>
+        <v>11111.111111111109</v>
       </c>
       <c r="J116" s="17">
         <f>E116*F116</f>
@@ -7386,23 +7161,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="16">
+    <row r="117" spans="1:11">
       <c r="A117" t="s">
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>439</v>
+        <v>123</v>
       </c>
       <c r="C117">
-        <v>13.67</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>10.85</v>
+        <v>0.4</v>
       </c>
       <c r="E117" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F117" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F117" s="13">
         <v>0</v>
       </c>
       <c r="G117" s="13">
@@ -7415,7 +7190,7 @@
       </c>
       <c r="I117" s="16">
         <f>E117/D117</f>
-        <v>423.963133640553</v>
+        <v>11250</v>
       </c>
       <c r="J117" s="17">
         <f>E117*F117</f>
@@ -7426,23 +7201,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="16">
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
         <v>3</v>
       </c>
       <c r="B118" t="s">
-        <v>458</v>
+        <v>500</v>
       </c>
       <c r="C118">
-        <v>10.039999999999999</v>
+        <v>2</v>
       </c>
       <c r="D118">
-        <v>10.58</v>
+        <v>0.35</v>
       </c>
       <c r="E118" s="3">
         <v>4500</v>
       </c>
-      <c r="F118" s="15">
+      <c r="F118" s="13">
         <v>0</v>
       </c>
       <c r="G118" s="13">
@@ -7455,7 +7230,7 @@
       </c>
       <c r="I118" s="16">
         <f>E118/D118</f>
-        <v>425.33081285444234</v>
+        <v>12857.142857142859</v>
       </c>
       <c r="J118" s="17">
         <f>E118*F118</f>
@@ -7466,23 +7241,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="16">
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
         <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>543</v>
+        <v>119</v>
       </c>
       <c r="C119">
-        <v>8.35</v>
+        <v>0.73</v>
       </c>
       <c r="D119">
-        <v>10.47</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E119" s="3">
         <v>4500</v>
       </c>
-      <c r="F119" s="15">
+      <c r="F119" s="13">
         <v>0</v>
       </c>
       <c r="G119" s="13">
@@ -7495,7 +7270,7 @@
       </c>
       <c r="I119" s="16">
         <f>E119/D119</f>
-        <v>429.79942693409737</v>
+        <v>15517.241379310346</v>
       </c>
       <c r="J119" s="17">
         <f>E119*F119</f>
@@ -7506,23 +7281,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="16">
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>378</v>
+        <v>479</v>
       </c>
       <c r="C120">
-        <v>10.73</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D120">
-        <v>10.46</v>
+        <v>0.11</v>
       </c>
       <c r="E120" s="3">
         <v>4500</v>
       </c>
-      <c r="F120" s="15">
+      <c r="F120" s="13">
         <v>0</v>
       </c>
       <c r="G120" s="13">
@@ -7535,7 +7310,7 @@
       </c>
       <c r="I120" s="16">
         <f>E120/D120</f>
-        <v>430.21032504780112</v>
+        <v>40909.090909090912</v>
       </c>
       <c r="J120" s="17">
         <f>E120*F120</f>
@@ -7546,23 +7321,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="16">
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>3</v>
       </c>
       <c r="B121" t="s">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="C121">
-        <v>11.05</v>
+        <v>0.47</v>
       </c>
       <c r="D121">
-        <v>10.3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E121" s="3">
         <v>4500</v>
       </c>
-      <c r="F121" s="15">
+      <c r="F121" s="13">
         <v>0</v>
       </c>
       <c r="G121" s="13">
@@ -7575,7 +7350,7 @@
       </c>
       <c r="I121" s="16">
         <f>E121/D121</f>
-        <v>436.89320388349512</v>
+        <v>64285.714285714283</v>
       </c>
       <c r="J121" s="17">
         <f>E121*F121</f>
@@ -7586,23 +7361,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="16">
+    <row r="122" spans="1:11">
       <c r="A122" t="s">
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>569</v>
+        <v>478</v>
       </c>
       <c r="C122">
-        <v>10.74</v>
+        <v>0.78</v>
       </c>
       <c r="D122">
-        <v>10.19</v>
+        <v>0.03</v>
       </c>
       <c r="E122" s="3">
         <v>4500</v>
       </c>
-      <c r="F122" s="15">
+      <c r="F122" s="13">
         <v>0</v>
       </c>
       <c r="G122" s="13">
@@ -7615,7 +7390,7 @@
       </c>
       <c r="I122" s="16">
         <f>E122/D122</f>
-        <v>441.6094210009814</v>
+        <v>150000</v>
       </c>
       <c r="J122" s="17">
         <f>E122*F122</f>
@@ -7626,3133 +7401,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="16">
-      <c r="A123" t="s">
-        <v>3</v>
-      </c>
-      <c r="B123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C123">
-        <v>12.38</v>
-      </c>
-      <c r="D123">
-        <v>10.97</v>
-      </c>
-      <c r="E123" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F123" s="15">
-        <v>0</v>
-      </c>
-      <c r="G123" s="13">
-        <f>IF(A123="G",1,0)*F123</f>
-        <v>0</v>
-      </c>
-      <c r="H123" s="13">
-        <f>IF(A123="F",1,0)*F123</f>
-        <v>0</v>
-      </c>
-      <c r="I123" s="16">
-        <f>E123/D123</f>
-        <v>446.67274384685504</v>
-      </c>
-      <c r="J123" s="17">
-        <f>E123*F123</f>
-        <v>0</v>
-      </c>
-      <c r="K123" s="13">
-        <f>F123*D123</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="16">
-      <c r="A124" t="s">
-        <v>3</v>
-      </c>
-      <c r="B124" t="s">
-        <v>525</v>
-      </c>
-      <c r="C124">
-        <v>9.93</v>
-      </c>
-      <c r="D124">
-        <v>9.9700000000000006</v>
-      </c>
-      <c r="E124" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F124" s="15">
-        <v>0</v>
-      </c>
-      <c r="G124" s="13">
-        <f>IF(A124="G",1,0)*F124</f>
-        <v>0</v>
-      </c>
-      <c r="H124" s="13">
-        <f>IF(A124="F",1,0)*F124</f>
-        <v>0</v>
-      </c>
-      <c r="I124" s="16">
-        <f>E124/D124</f>
-        <v>451.35406218655964</v>
-      </c>
-      <c r="J124" s="17">
-        <f>E124*F124</f>
-        <v>0</v>
-      </c>
-      <c r="K124" s="13">
-        <f>F124*D124</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="16">
-      <c r="A125" t="s">
-        <v>0</v>
-      </c>
-      <c r="B125" t="s">
-        <v>514</v>
-      </c>
-      <c r="C125">
-        <v>14.82</v>
-      </c>
-      <c r="D125">
-        <v>10.87</v>
-      </c>
-      <c r="E125" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F125" s="15">
-        <v>0</v>
-      </c>
-      <c r="G125" s="13">
-        <f>IF(A125="G",1,0)*F125</f>
-        <v>0</v>
-      </c>
-      <c r="H125" s="13">
-        <f>IF(A125="F",1,0)*F125</f>
-        <v>0</v>
-      </c>
-      <c r="I125" s="16">
-        <f>E125/D125</f>
-        <v>459.98160073597057</v>
-      </c>
-      <c r="J125" s="17">
-        <f>E125*F125</f>
-        <v>0</v>
-      </c>
-      <c r="K125" s="13">
-        <f>F125*D125</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="16">
-      <c r="A126" t="s">
-        <v>3</v>
-      </c>
-      <c r="B126" t="s">
-        <v>539</v>
-      </c>
-      <c r="C126">
-        <v>10.6</v>
-      </c>
-      <c r="D126">
-        <v>9.7799999999999994</v>
-      </c>
-      <c r="E126" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F126" s="15">
-        <v>0</v>
-      </c>
-      <c r="G126" s="13">
-        <f>IF(A126="G",1,0)*F126</f>
-        <v>0</v>
-      </c>
-      <c r="H126" s="13">
-        <f>IF(A126="F",1,0)*F126</f>
-        <v>0</v>
-      </c>
-      <c r="I126" s="16">
-        <f>E126/D126</f>
-        <v>460.12269938650309</v>
-      </c>
-      <c r="J126" s="17">
-        <f>E126*F126</f>
-        <v>0</v>
-      </c>
-      <c r="K126" s="13">
-        <f>F126*D126</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="16">
-      <c r="A127" t="s">
-        <v>3</v>
-      </c>
-      <c r="B127" t="s">
-        <v>321</v>
-      </c>
-      <c r="C127">
-        <v>12.35</v>
-      </c>
-      <c r="D127">
-        <v>10.62</v>
-      </c>
-      <c r="E127" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F127" s="15">
-        <v>0</v>
-      </c>
-      <c r="G127" s="13">
-        <f>IF(A127="G",1,0)*F127</f>
-        <v>0</v>
-      </c>
-      <c r="H127" s="13">
-        <f>IF(A127="F",1,0)*F127</f>
-        <v>0</v>
-      </c>
-      <c r="I127" s="16">
-        <f>E127/D127</f>
-        <v>461.39359698681739</v>
-      </c>
-      <c r="J127" s="17">
-        <f>E127*F127</f>
-        <v>0</v>
-      </c>
-      <c r="K127" s="13">
-        <f>F127*D127</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="16">
-      <c r="A128" t="s">
-        <v>0</v>
-      </c>
-      <c r="B128" t="s">
-        <v>68</v>
-      </c>
-      <c r="C128">
-        <v>8.1</v>
-      </c>
-      <c r="D128">
-        <v>9.75</v>
-      </c>
-      <c r="E128" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F128" s="15">
-        <v>0</v>
-      </c>
-      <c r="G128" s="13">
-        <f>IF(A128="G",1,0)*F128</f>
-        <v>0</v>
-      </c>
-      <c r="H128" s="13">
-        <f>IF(A128="F",1,0)*F128</f>
-        <v>0</v>
-      </c>
-      <c r="I128" s="16">
-        <f>E128/D128</f>
-        <v>461.53846153846155</v>
-      </c>
-      <c r="J128" s="17">
-        <f>E128*F128</f>
-        <v>0</v>
-      </c>
-      <c r="K128" s="13">
-        <f>F128*D128</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="16">
-      <c r="A129" t="s">
-        <v>3</v>
-      </c>
-      <c r="B129" t="s">
-        <v>556</v>
-      </c>
-      <c r="C129">
-        <v>12.01</v>
-      </c>
-      <c r="D129">
-        <v>9.49</v>
-      </c>
-      <c r="E129" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F129" s="15">
-        <v>0</v>
-      </c>
-      <c r="G129" s="13">
-        <f>IF(A129="G",1,0)*F129</f>
-        <v>0</v>
-      </c>
-      <c r="H129" s="13">
-        <f>IF(A129="F",1,0)*F129</f>
-        <v>0</v>
-      </c>
-      <c r="I129" s="16">
-        <f>E129/D129</f>
-        <v>474.18335089567967</v>
-      </c>
-      <c r="J129" s="17">
-        <f>E129*F129</f>
-        <v>0</v>
-      </c>
-      <c r="K129" s="13">
-        <f>F129*D129</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" ht="16">
-      <c r="A130" t="s">
-        <v>0</v>
-      </c>
-      <c r="B130" t="s">
-        <v>437</v>
-      </c>
-      <c r="C130">
-        <v>11.88</v>
-      </c>
-      <c r="D130">
-        <v>9.3800000000000008</v>
-      </c>
-      <c r="E130" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F130" s="15">
-        <v>0</v>
-      </c>
-      <c r="G130" s="13">
-        <f>IF(A130="G",1,0)*F130</f>
-        <v>0</v>
-      </c>
-      <c r="H130" s="13">
-        <f>IF(A130="F",1,0)*F130</f>
-        <v>0</v>
-      </c>
-      <c r="I130" s="16">
-        <f>E130/D130</f>
-        <v>479.74413646055433</v>
-      </c>
-      <c r="J130" s="17">
-        <f>E130*F130</f>
-        <v>0</v>
-      </c>
-      <c r="K130" s="13">
-        <f>F130*D130</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="16">
-      <c r="A131" t="s">
-        <v>0</v>
-      </c>
-      <c r="B131" t="s">
-        <v>534</v>
-      </c>
-      <c r="C131">
-        <v>9.09</v>
-      </c>
-      <c r="D131">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="E131" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F131" s="15">
-        <v>0</v>
-      </c>
-      <c r="G131" s="13">
-        <f>IF(A131="G",1,0)*F131</f>
-        <v>0</v>
-      </c>
-      <c r="H131" s="13">
-        <f>IF(A131="F",1,0)*F131</f>
-        <v>0</v>
-      </c>
-      <c r="I131" s="16">
-        <f>E131/D131</f>
-        <v>489.13043478260875</v>
-      </c>
-      <c r="J131" s="17">
-        <f>E131*F131</f>
-        <v>0</v>
-      </c>
-      <c r="K131" s="13">
-        <f>F131*D131</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="16">
-      <c r="A132" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" t="s">
-        <v>522</v>
-      </c>
-      <c r="C132">
-        <v>9.4</v>
-      </c>
-      <c r="D132">
-        <v>9.36</v>
-      </c>
-      <c r="E132" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F132" s="15">
-        <v>0</v>
-      </c>
-      <c r="G132" s="13">
-        <f>IF(A132="G",1,0)*F132</f>
-        <v>0</v>
-      </c>
-      <c r="H132" s="13">
-        <f>IF(A132="F",1,0)*F132</f>
-        <v>0</v>
-      </c>
-      <c r="I132" s="16">
-        <f>E132/D132</f>
-        <v>491.45299145299145</v>
-      </c>
-      <c r="J132" s="17">
-        <f>E132*F132</f>
-        <v>0</v>
-      </c>
-      <c r="K132" s="13">
-        <f>F132*D132</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="16">
-      <c r="A133" t="s">
-        <v>0</v>
-      </c>
-      <c r="B133" t="s">
-        <v>502</v>
-      </c>
-      <c r="C133">
-        <v>12.74</v>
-      </c>
-      <c r="D133">
-        <v>11.08</v>
-      </c>
-      <c r="E133" s="3">
-        <v>5600</v>
-      </c>
-      <c r="F133" s="15">
-        <v>0</v>
-      </c>
-      <c r="G133" s="13">
-        <f>IF(A133="G",1,0)*F133</f>
-        <v>0</v>
-      </c>
-      <c r="H133" s="13">
-        <f>IF(A133="F",1,0)*F133</f>
-        <v>0</v>
-      </c>
-      <c r="I133" s="16">
-        <f>E133/D133</f>
-        <v>505.41516245487367</v>
-      </c>
-      <c r="J133" s="17">
-        <f>E133*F133</f>
-        <v>0</v>
-      </c>
-      <c r="K133" s="13">
-        <f>F133*D133</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="16">
-      <c r="A134" t="s">
-        <v>0</v>
-      </c>
-      <c r="B134" t="s">
-        <v>546</v>
-      </c>
-      <c r="C134">
-        <v>7.2</v>
-      </c>
-      <c r="D134">
-        <v>8.68</v>
-      </c>
-      <c r="E134" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F134" s="15">
-        <v>0</v>
-      </c>
-      <c r="G134" s="13">
-        <f>IF(A134="G",1,0)*F134</f>
-        <v>0</v>
-      </c>
-      <c r="H134" s="13">
-        <f>IF(A134="F",1,0)*F134</f>
-        <v>0</v>
-      </c>
-      <c r="I134" s="16">
-        <f>E134/D134</f>
-        <v>518.43317972350235</v>
-      </c>
-      <c r="J134" s="17">
-        <f>E134*F134</f>
-        <v>0</v>
-      </c>
-      <c r="K134" s="13">
-        <f>F134*D134</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="16">
-      <c r="A135" t="s">
-        <v>0</v>
-      </c>
-      <c r="B135" t="s">
-        <v>537</v>
-      </c>
-      <c r="C135">
-        <v>8.73</v>
-      </c>
-      <c r="D135">
-        <v>8.49</v>
-      </c>
-      <c r="E135" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F135" s="15">
-        <v>0</v>
-      </c>
-      <c r="G135" s="13">
-        <f>IF(A135="G",1,0)*F135</f>
-        <v>0</v>
-      </c>
-      <c r="H135" s="13">
-        <f>IF(A135="F",1,0)*F135</f>
-        <v>0</v>
-      </c>
-      <c r="I135" s="16">
-        <f>E135/D135</f>
-        <v>530.03533568904595</v>
-      </c>
-      <c r="J135" s="17">
-        <f>E135*F135</f>
-        <v>0</v>
-      </c>
-      <c r="K135" s="13">
-        <f>F135*D135</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="16">
-      <c r="A136" t="s">
-        <v>3</v>
-      </c>
-      <c r="B136" t="s">
-        <v>445</v>
-      </c>
-      <c r="C136">
-        <v>6.44</v>
-      </c>
-      <c r="D136">
-        <v>8.25</v>
-      </c>
-      <c r="E136" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F136" s="15">
-        <v>0</v>
-      </c>
-      <c r="G136" s="13">
-        <f>IF(A136="G",1,0)*F136</f>
-        <v>0</v>
-      </c>
-      <c r="H136" s="13">
-        <f>IF(A136="F",1,0)*F136</f>
-        <v>0</v>
-      </c>
-      <c r="I136" s="16">
-        <f>E136/D136</f>
-        <v>545.4545454545455</v>
-      </c>
-      <c r="J136" s="17">
-        <f>E136*F136</f>
-        <v>0</v>
-      </c>
-      <c r="K136" s="13">
-        <f>F136*D136</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" ht="16">
-      <c r="A137" t="s">
-        <v>3</v>
-      </c>
-      <c r="B137" t="s">
-        <v>429</v>
-      </c>
-      <c r="C137">
-        <v>10.65</v>
-      </c>
-      <c r="D137">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="E137" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F137" s="15">
-        <v>0</v>
-      </c>
-      <c r="G137" s="13">
-        <f>IF(A137="G",1,0)*F137</f>
-        <v>0</v>
-      </c>
-      <c r="H137" s="13">
-        <f>IF(A137="F",1,0)*F137</f>
-        <v>0</v>
-      </c>
-      <c r="I137" s="16">
-        <f>E137/D137</f>
-        <v>551.80180180180173</v>
-      </c>
-      <c r="J137" s="17">
-        <f>E137*F137</f>
-        <v>0</v>
-      </c>
-      <c r="K137" s="13">
-        <f>F137*D137</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="16">
-      <c r="A138" t="s">
-        <v>0</v>
-      </c>
-      <c r="B138" t="s">
-        <v>577</v>
-      </c>
-      <c r="C138">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="D138">
-        <v>8.06</v>
-      </c>
-      <c r="E138" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F138" s="15">
-        <v>0</v>
-      </c>
-      <c r="G138" s="13">
-        <f>IF(A138="G",1,0)*F138</f>
-        <v>0</v>
-      </c>
-      <c r="H138" s="13">
-        <f>IF(A138="F",1,0)*F138</f>
-        <v>0</v>
-      </c>
-      <c r="I138" s="16">
-        <f>E138/D138</f>
-        <v>558.31265508684862</v>
-      </c>
-      <c r="J138" s="17">
-        <f>E138*F138</f>
-        <v>0</v>
-      </c>
-      <c r="K138" s="13">
-        <f>F138*D138</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="16">
-      <c r="A139" t="s">
-        <v>3</v>
-      </c>
-      <c r="B139" t="s">
-        <v>406</v>
-      </c>
-      <c r="C139">
-        <v>14.44</v>
-      </c>
-      <c r="D139">
-        <v>13.58</v>
-      </c>
-      <c r="E139" s="3">
-        <v>7700</v>
-      </c>
-      <c r="F139" s="15">
-        <v>0</v>
-      </c>
-      <c r="G139" s="13">
-        <f>IF(A139="G",1,0)*F139</f>
-        <v>0</v>
-      </c>
-      <c r="H139" s="13">
-        <f>IF(A139="F",1,0)*F139</f>
-        <v>0</v>
-      </c>
-      <c r="I139" s="16">
-        <f>E139/D139</f>
-        <v>567.01030927835052</v>
-      </c>
-      <c r="J139" s="17">
-        <f>E139*F139</f>
-        <v>0</v>
-      </c>
-      <c r="K139" s="13">
-        <f>F139*D139</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="16">
-      <c r="A140" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" t="s">
-        <v>536</v>
-      </c>
-      <c r="C140">
-        <v>7.68</v>
-      </c>
-      <c r="D140">
-        <v>7.93</v>
-      </c>
-      <c r="E140" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F140" s="15">
-        <v>0</v>
-      </c>
-      <c r="G140" s="13">
-        <f>IF(A140="G",1,0)*F140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="13">
-        <f>IF(A140="F",1,0)*F140</f>
-        <v>0</v>
-      </c>
-      <c r="I140" s="16">
-        <f>E140/D140</f>
-        <v>567.46532156368221</v>
-      </c>
-      <c r="J140" s="17">
-        <f>E140*F140</f>
-        <v>0</v>
-      </c>
-      <c r="K140" s="13">
-        <f>F140*D140</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" ht="16">
-      <c r="A141" t="s">
-        <v>0</v>
-      </c>
-      <c r="B141" t="s">
-        <v>435</v>
-      </c>
-      <c r="C141">
-        <v>10.26</v>
-      </c>
-      <c r="D141">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="E141" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F141" s="15">
-        <v>0</v>
-      </c>
-      <c r="G141" s="13">
-        <f>IF(A141="G",1,0)*F141</f>
-        <v>0</v>
-      </c>
-      <c r="H141" s="13">
-        <f>IF(A141="F",1,0)*F141</f>
-        <v>0</v>
-      </c>
-      <c r="I141" s="16">
-        <f>E141/D141</f>
-        <v>568.82821387940851</v>
-      </c>
-      <c r="J141" s="17">
-        <f>E141*F141</f>
-        <v>0</v>
-      </c>
-      <c r="K141" s="13">
-        <f>F141*D141</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="16">
-      <c r="A142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B142" t="s">
-        <v>559</v>
-      </c>
-      <c r="C142">
-        <v>8.5</v>
-      </c>
-      <c r="D142">
-        <v>7.9</v>
-      </c>
-      <c r="E142" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F142" s="15">
-        <v>0</v>
-      </c>
-      <c r="G142" s="13">
-        <f>IF(A142="G",1,0)*F142</f>
-        <v>0</v>
-      </c>
-      <c r="H142" s="13">
-        <f>IF(A142="F",1,0)*F142</f>
-        <v>0</v>
-      </c>
-      <c r="I142" s="16">
-        <f>E142/D142</f>
-        <v>569.62025316455697</v>
-      </c>
-      <c r="J142" s="17">
-        <f>E142*F142</f>
-        <v>0</v>
-      </c>
-      <c r="K142" s="13">
-        <f>F142*D142</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" ht="16">
-      <c r="A143" t="s">
-        <v>3</v>
-      </c>
-      <c r="B143" t="s">
-        <v>455</v>
-      </c>
-      <c r="C143">
-        <v>9.69</v>
-      </c>
-      <c r="D143">
-        <v>7.7</v>
-      </c>
-      <c r="E143" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F143" s="15">
-        <v>0</v>
-      </c>
-      <c r="G143" s="13">
-        <f>IF(A143="G",1,0)*F143</f>
-        <v>0</v>
-      </c>
-      <c r="H143" s="13">
-        <f>IF(A143="F",1,0)*F143</f>
-        <v>0</v>
-      </c>
-      <c r="I143" s="16">
-        <f>E143/D143</f>
-        <v>584.41558441558436</v>
-      </c>
-      <c r="J143" s="17">
-        <f>E143*F143</f>
-        <v>0</v>
-      </c>
-      <c r="K143" s="13">
-        <f>F143*D143</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="16">
-      <c r="A144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B144" t="s">
-        <v>466</v>
-      </c>
-      <c r="C144">
-        <v>8.1199999999999992</v>
-      </c>
-      <c r="D144">
-        <v>7.47</v>
-      </c>
-      <c r="E144" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F144" s="15">
-        <v>0</v>
-      </c>
-      <c r="G144" s="13">
-        <f>IF(A144="G",1,0)*F144</f>
-        <v>0</v>
-      </c>
-      <c r="H144" s="13">
-        <f>IF(A144="F",1,0)*F144</f>
-        <v>0</v>
-      </c>
-      <c r="I144" s="16">
-        <f>E144/D144</f>
-        <v>602.40963855421694</v>
-      </c>
-      <c r="J144" s="17">
-        <f>E144*F144</f>
-        <v>0</v>
-      </c>
-      <c r="K144" s="13">
-        <f>F144*D144</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="16">
-      <c r="A145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" t="s">
-        <v>520</v>
-      </c>
-      <c r="C145">
-        <v>9.64</v>
-      </c>
-      <c r="D145">
-        <v>7.67</v>
-      </c>
-      <c r="E145" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F145" s="15">
-        <v>0</v>
-      </c>
-      <c r="G145" s="13">
-        <f>IF(A145="G",1,0)*F145</f>
-        <v>0</v>
-      </c>
-      <c r="H145" s="13">
-        <f>IF(A145="F",1,0)*F145</f>
-        <v>0</v>
-      </c>
-      <c r="I145" s="16">
-        <f>E145/D145</f>
-        <v>612.77705345501954</v>
-      </c>
-      <c r="J145" s="17">
-        <f>E145*F145</f>
-        <v>0</v>
-      </c>
-      <c r="K145" s="13">
-        <f>F145*D145</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="16">
-      <c r="A146" t="s">
-        <v>3</v>
-      </c>
-      <c r="B146" t="s">
-        <v>566</v>
-      </c>
-      <c r="C146">
-        <v>6.91</v>
-      </c>
-      <c r="D146">
-        <v>7.32</v>
-      </c>
-      <c r="E146" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F146" s="15">
-        <v>0</v>
-      </c>
-      <c r="G146" s="13">
-        <f>IF(A146="G",1,0)*F146</f>
-        <v>0</v>
-      </c>
-      <c r="H146" s="13">
-        <f>IF(A146="F",1,0)*F146</f>
-        <v>0</v>
-      </c>
-      <c r="I146" s="16">
-        <f>E146/D146</f>
-        <v>614.75409836065569</v>
-      </c>
-      <c r="J146" s="17">
-        <f>E146*F146</f>
-        <v>0</v>
-      </c>
-      <c r="K146" s="13">
-        <f>F146*D146</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="16">
-      <c r="A147" t="s">
-        <v>3</v>
-      </c>
-      <c r="B147" t="s">
-        <v>552</v>
-      </c>
-      <c r="C147">
-        <v>5.46</v>
-      </c>
-      <c r="D147">
-        <v>7.17</v>
-      </c>
-      <c r="E147" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F147" s="15">
-        <v>0</v>
-      </c>
-      <c r="G147" s="13">
-        <f>IF(A147="G",1,0)*F147</f>
-        <v>0</v>
-      </c>
-      <c r="H147" s="13">
-        <f>IF(A147="F",1,0)*F147</f>
-        <v>0</v>
-      </c>
-      <c r="I147" s="16">
-        <f>E147/D147</f>
-        <v>627.61506276150624</v>
-      </c>
-      <c r="J147" s="17">
-        <f>E147*F147</f>
-        <v>0</v>
-      </c>
-      <c r="K147" s="13">
-        <f>F147*D147</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" ht="16">
-      <c r="A148" t="s">
-        <v>3</v>
-      </c>
-      <c r="B148" t="s">
-        <v>434</v>
-      </c>
-      <c r="C148">
-        <v>9.19</v>
-      </c>
-      <c r="D148">
-        <v>7.16</v>
-      </c>
-      <c r="E148" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F148" s="15">
-        <v>0</v>
-      </c>
-      <c r="G148" s="13">
-        <f>IF(A148="G",1,0)*F148</f>
-        <v>0</v>
-      </c>
-      <c r="H148" s="13">
-        <f>IF(A148="F",1,0)*F148</f>
-        <v>0</v>
-      </c>
-      <c r="I148" s="16">
-        <f>E148/D148</f>
-        <v>628.49162011173178</v>
-      </c>
-      <c r="J148" s="17">
-        <f>E148*F148</f>
-        <v>0</v>
-      </c>
-      <c r="K148" s="13">
-        <f>F148*D148</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="16">
-      <c r="A149" t="s">
-        <v>0</v>
-      </c>
-      <c r="B149" t="s">
-        <v>463</v>
-      </c>
-      <c r="C149">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="D149">
-        <v>7.13</v>
-      </c>
-      <c r="E149" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F149" s="15">
-        <v>0</v>
-      </c>
-      <c r="G149" s="13">
-        <f>IF(A149="G",1,0)*F149</f>
-        <v>0</v>
-      </c>
-      <c r="H149" s="13">
-        <f>IF(A149="F",1,0)*F149</f>
-        <v>0</v>
-      </c>
-      <c r="I149" s="16">
-        <f>E149/D149</f>
-        <v>631.13604488078545</v>
-      </c>
-      <c r="J149" s="17">
-        <f>E149*F149</f>
-        <v>0</v>
-      </c>
-      <c r="K149" s="13">
-        <f>F149*D149</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" ht="16">
-      <c r="A150" t="s">
-        <v>0</v>
-      </c>
-      <c r="B150" t="s">
-        <v>96</v>
-      </c>
-      <c r="C150">
-        <v>6.95</v>
-      </c>
-      <c r="D150">
-        <v>7.12</v>
-      </c>
-      <c r="E150" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F150" s="15">
-        <v>0</v>
-      </c>
-      <c r="G150" s="13">
-        <f>IF(A150="G",1,0)*F150</f>
-        <v>0</v>
-      </c>
-      <c r="H150" s="13">
-        <f>IF(A150="F",1,0)*F150</f>
-        <v>0</v>
-      </c>
-      <c r="I150" s="16">
-        <f>E150/D150</f>
-        <v>632.02247191011236</v>
-      </c>
-      <c r="J150" s="17">
-        <f>E150*F150</f>
-        <v>0</v>
-      </c>
-      <c r="K150" s="13">
-        <f>F150*D150</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" ht="16">
-      <c r="A151" t="s">
-        <v>3</v>
-      </c>
-      <c r="B151" t="s">
-        <v>531</v>
-      </c>
-      <c r="C151">
-        <v>6.47</v>
-      </c>
-      <c r="D151">
-        <v>6.86</v>
-      </c>
-      <c r="E151" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F151" s="15">
-        <v>0</v>
-      </c>
-      <c r="G151" s="13">
-        <f>IF(A151="G",1,0)*F151</f>
-        <v>0</v>
-      </c>
-      <c r="H151" s="13">
-        <f>IF(A151="F",1,0)*F151</f>
-        <v>0</v>
-      </c>
-      <c r="I151" s="16">
-        <f>E151/D151</f>
-        <v>655.97667638483961</v>
-      </c>
-      <c r="J151" s="17">
-        <f>E151*F151</f>
-        <v>0</v>
-      </c>
-      <c r="K151" s="13">
-        <f>F151*D151</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" ht="16">
-      <c r="A152" t="s">
-        <v>0</v>
-      </c>
-      <c r="B152" t="s">
-        <v>565</v>
-      </c>
-      <c r="C152">
-        <v>7.92</v>
-      </c>
-      <c r="D152">
-        <v>6.61</v>
-      </c>
-      <c r="E152" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F152" s="15">
-        <v>0</v>
-      </c>
-      <c r="G152" s="13">
-        <f>IF(A152="G",1,0)*F152</f>
-        <v>0</v>
-      </c>
-      <c r="H152" s="13">
-        <f>IF(A152="F",1,0)*F152</f>
-        <v>0</v>
-      </c>
-      <c r="I152" s="16">
-        <f>E152/D152</f>
-        <v>680.78668683812407</v>
-      </c>
-      <c r="J152" s="17">
-        <f>E152*F152</f>
-        <v>0</v>
-      </c>
-      <c r="K152" s="13">
-        <f>F152*D152</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" ht="16">
-      <c r="A153" t="s">
-        <v>3</v>
-      </c>
-      <c r="B153" t="s">
-        <v>538</v>
-      </c>
-      <c r="C153">
-        <v>5.41</v>
-      </c>
-      <c r="D153">
-        <v>6.58</v>
-      </c>
-      <c r="E153" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F153" s="15">
-        <v>0</v>
-      </c>
-      <c r="G153" s="13">
-        <f>IF(A153="G",1,0)*F153</f>
-        <v>0</v>
-      </c>
-      <c r="H153" s="13">
-        <f>IF(A153="F",1,0)*F153</f>
-        <v>0</v>
-      </c>
-      <c r="I153" s="16">
-        <f>E153/D153</f>
-        <v>683.89057750759878</v>
-      </c>
-      <c r="J153" s="17">
-        <f>E153*F153</f>
-        <v>0</v>
-      </c>
-      <c r="K153" s="13">
-        <f>F153*D153</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" ht="16">
-      <c r="A154" t="s">
-        <v>3</v>
-      </c>
-      <c r="B154" t="s">
-        <v>550</v>
-      </c>
-      <c r="C154">
-        <v>6.5</v>
-      </c>
-      <c r="D154">
-        <v>6.54</v>
-      </c>
-      <c r="E154" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F154" s="15">
-        <v>0</v>
-      </c>
-      <c r="G154" s="13">
-        <f>IF(A154="G",1,0)*F154</f>
-        <v>0</v>
-      </c>
-      <c r="H154" s="13">
-        <f>IF(A154="F",1,0)*F154</f>
-        <v>0</v>
-      </c>
-      <c r="I154" s="16">
-        <f>E154/D154</f>
-        <v>688.0733944954128</v>
-      </c>
-      <c r="J154" s="17">
-        <f>E154*F154</f>
-        <v>0</v>
-      </c>
-      <c r="K154" s="13">
-        <f>F154*D154</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" ht="16">
-      <c r="A155" t="s">
-        <v>0</v>
-      </c>
-      <c r="B155" t="s">
-        <v>578</v>
-      </c>
-      <c r="C155">
-        <v>9.44</v>
-      </c>
-      <c r="D155">
-        <v>6.49</v>
-      </c>
-      <c r="E155" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F155" s="15">
-        <v>0</v>
-      </c>
-      <c r="G155" s="13">
-        <f>IF(A155="G",1,0)*F155</f>
-        <v>0</v>
-      </c>
-      <c r="H155" s="13">
-        <f>IF(A155="F",1,0)*F155</f>
-        <v>0</v>
-      </c>
-      <c r="I155" s="16">
-        <f>E155/D155</f>
-        <v>693.37442218798151</v>
-      </c>
-      <c r="J155" s="17">
-        <f>E155*F155</f>
-        <v>0</v>
-      </c>
-      <c r="K155" s="13">
-        <f>F155*D155</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" ht="16">
-      <c r="A156" t="s">
-        <v>3</v>
-      </c>
-      <c r="B156" t="s">
-        <v>554</v>
-      </c>
-      <c r="C156">
-        <v>9.41</v>
-      </c>
-      <c r="D156">
-        <v>6.39</v>
-      </c>
-      <c r="E156" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F156" s="15">
-        <v>0</v>
-      </c>
-      <c r="G156" s="13">
-        <f>IF(A156="G",1,0)*F156</f>
-        <v>0</v>
-      </c>
-      <c r="H156" s="13">
-        <f>IF(A156="F",1,0)*F156</f>
-        <v>0</v>
-      </c>
-      <c r="I156" s="16">
-        <f>E156/D156</f>
-        <v>704.22535211267609</v>
-      </c>
-      <c r="J156" s="17">
-        <f>E156*F156</f>
-        <v>0</v>
-      </c>
-      <c r="K156" s="13">
-        <f>F156*D156</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" ht="16">
-      <c r="A157" t="s">
-        <v>3</v>
-      </c>
-      <c r="B157" t="s">
-        <v>545</v>
-      </c>
-      <c r="C157">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="D157">
-        <v>6.3</v>
-      </c>
-      <c r="E157" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F157" s="15">
-        <v>0</v>
-      </c>
-      <c r="G157" s="13">
-        <f>IF(A157="G",1,0)*F157</f>
-        <v>0</v>
-      </c>
-      <c r="H157" s="13">
-        <f>IF(A157="F",1,0)*F157</f>
-        <v>0</v>
-      </c>
-      <c r="I157" s="16">
-        <f>E157/D157</f>
-        <v>714.28571428571433</v>
-      </c>
-      <c r="J157" s="17">
-        <f>E157*F157</f>
-        <v>0</v>
-      </c>
-      <c r="K157" s="13">
-        <f>F157*D157</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" ht="16">
-      <c r="A158" t="s">
-        <v>3</v>
-      </c>
-      <c r="B158" t="s">
-        <v>446</v>
-      </c>
-      <c r="C158">
-        <v>5.3</v>
-      </c>
-      <c r="D158">
-        <v>6.25</v>
-      </c>
-      <c r="E158" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F158" s="15">
-        <v>0</v>
-      </c>
-      <c r="G158" s="13">
-        <f>IF(A158="G",1,0)*F158</f>
-        <v>0</v>
-      </c>
-      <c r="H158" s="13">
-        <f>IF(A158="F",1,0)*F158</f>
-        <v>0</v>
-      </c>
-      <c r="I158" s="16">
-        <f>E158/D158</f>
-        <v>720</v>
-      </c>
-      <c r="J158" s="17">
-        <f>E158*F158</f>
-        <v>0</v>
-      </c>
-      <c r="K158" s="13">
-        <f>F158*D158</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" ht="16">
-      <c r="A159" t="s">
-        <v>0</v>
-      </c>
-      <c r="B159" t="s">
-        <v>574</v>
-      </c>
-      <c r="C159">
-        <v>5.87</v>
-      </c>
-      <c r="D159">
-        <v>6.25</v>
-      </c>
-      <c r="E159" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F159" s="15">
-        <v>0</v>
-      </c>
-      <c r="G159" s="13">
-        <f>IF(A159="G",1,0)*F159</f>
-        <v>0</v>
-      </c>
-      <c r="H159" s="13">
-        <f>IF(A159="F",1,0)*F159</f>
-        <v>0</v>
-      </c>
-      <c r="I159" s="16">
-        <f>E159/D159</f>
-        <v>720</v>
-      </c>
-      <c r="J159" s="17">
-        <f>E159*F159</f>
-        <v>0</v>
-      </c>
-      <c r="K159" s="13">
-        <f>F159*D159</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" ht="16">
-      <c r="A160" t="s">
-        <v>0</v>
-      </c>
-      <c r="B160" t="s">
-        <v>459</v>
-      </c>
-      <c r="C160">
-        <v>5.25</v>
-      </c>
-      <c r="D160">
-        <v>6.24</v>
-      </c>
-      <c r="E160" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F160" s="15">
-        <v>0</v>
-      </c>
-      <c r="G160" s="13">
-        <f>IF(A160="G",1,0)*F160</f>
-        <v>0</v>
-      </c>
-      <c r="H160" s="13">
-        <f>IF(A160="F",1,0)*F160</f>
-        <v>0</v>
-      </c>
-      <c r="I160" s="16">
-        <f>E160/D160</f>
-        <v>721.15384615384608</v>
-      </c>
-      <c r="J160" s="17">
-        <f>E160*F160</f>
-        <v>0</v>
-      </c>
-      <c r="K160" s="13">
-        <f>F160*D160</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="16">
-      <c r="A161" t="s">
-        <v>3</v>
-      </c>
-      <c r="B161" t="s">
-        <v>555</v>
-      </c>
-      <c r="C161">
-        <v>7.29</v>
-      </c>
-      <c r="D161">
-        <v>6.21</v>
-      </c>
-      <c r="E161" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F161" s="15">
-        <v>0</v>
-      </c>
-      <c r="G161" s="13">
-        <f>IF(A161="G",1,0)*F161</f>
-        <v>0</v>
-      </c>
-      <c r="H161" s="13">
-        <f>IF(A161="F",1,0)*F161</f>
-        <v>0</v>
-      </c>
-      <c r="I161" s="16">
-        <f>E161/D161</f>
-        <v>724.63768115942025</v>
-      </c>
-      <c r="J161" s="17">
-        <f>E161*F161</f>
-        <v>0</v>
-      </c>
-      <c r="K161" s="13">
-        <f>F161*D161</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" ht="16">
-      <c r="A162" t="s">
-        <v>0</v>
-      </c>
-      <c r="B162" t="s">
-        <v>436</v>
-      </c>
-      <c r="C162">
-        <v>8.23</v>
-      </c>
-      <c r="D162">
-        <v>6.46</v>
-      </c>
-      <c r="E162" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F162" s="15">
-        <v>0</v>
-      </c>
-      <c r="G162" s="13">
-        <f>IF(A162="G",1,0)*F162</f>
-        <v>0</v>
-      </c>
-      <c r="H162" s="13">
-        <f>IF(A162="F",1,0)*F162</f>
-        <v>0</v>
-      </c>
-      <c r="I162" s="16">
-        <f>E162/D162</f>
-        <v>743.03405572755423</v>
-      </c>
-      <c r="J162" s="17">
-        <f>E162*F162</f>
-        <v>0</v>
-      </c>
-      <c r="K162" s="13">
-        <f>F162*D162</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="16">
-      <c r="A163" t="s">
-        <v>0</v>
-      </c>
-      <c r="B163" t="s">
-        <v>516</v>
-      </c>
-      <c r="C163">
-        <v>6.84</v>
-      </c>
-      <c r="D163">
-        <v>6.41</v>
-      </c>
-      <c r="E163" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F163" s="15">
-        <v>0</v>
-      </c>
-      <c r="G163" s="13">
-        <f>IF(A163="G",1,0)*F163</f>
-        <v>0</v>
-      </c>
-      <c r="H163" s="13">
-        <f>IF(A163="F",1,0)*F163</f>
-        <v>0</v>
-      </c>
-      <c r="I163" s="16">
-        <f>E163/D163</f>
-        <v>748.8299531981279</v>
-      </c>
-      <c r="J163" s="17">
-        <f>E163*F163</f>
-        <v>0</v>
-      </c>
-      <c r="K163" s="13">
-        <f>F163*D163</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" ht="16">
-      <c r="A164" t="s">
-        <v>3</v>
-      </c>
-      <c r="B164" t="s">
-        <v>460</v>
-      </c>
-      <c r="C164">
-        <v>7.94</v>
-      </c>
-      <c r="D164">
-        <v>6.05</v>
-      </c>
-      <c r="E164" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F164" s="15">
-        <v>0</v>
-      </c>
-      <c r="G164" s="13">
-        <f>IF(A164="G",1,0)*F164</f>
-        <v>0</v>
-      </c>
-      <c r="H164" s="13">
-        <f>IF(A164="F",1,0)*F164</f>
-        <v>0</v>
-      </c>
-      <c r="I164" s="16">
-        <f>E164/D164</f>
-        <v>760.33057851239676</v>
-      </c>
-      <c r="J164" s="17">
-        <f>E164*F164</f>
-        <v>0</v>
-      </c>
-      <c r="K164" s="13">
-        <f>F164*D164</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" ht="16">
-      <c r="A165" t="s">
-        <v>3</v>
-      </c>
-      <c r="B165" t="s">
-        <v>533</v>
-      </c>
-      <c r="C165">
-        <v>6.8</v>
-      </c>
-      <c r="D165">
-        <v>5.81</v>
-      </c>
-      <c r="E165" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F165" s="15">
-        <v>0</v>
-      </c>
-      <c r="G165" s="13">
-        <f>IF(A165="G",1,0)*F165</f>
-        <v>0</v>
-      </c>
-      <c r="H165" s="13">
-        <f>IF(A165="F",1,0)*F165</f>
-        <v>0</v>
-      </c>
-      <c r="I165" s="16">
-        <f>E165/D165</f>
-        <v>774.52667814113602</v>
-      </c>
-      <c r="J165" s="17">
-        <f>E165*F165</f>
-        <v>0</v>
-      </c>
-      <c r="K165" s="13">
-        <f>F165*D165</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" ht="16">
-      <c r="A166" t="s">
-        <v>3</v>
-      </c>
-      <c r="B166" t="s">
-        <v>547</v>
-      </c>
-      <c r="C166">
-        <v>7.4</v>
-      </c>
-      <c r="D166">
-        <v>5.8</v>
-      </c>
-      <c r="E166" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F166" s="15">
-        <v>0</v>
-      </c>
-      <c r="G166" s="13">
-        <f>IF(A166="G",1,0)*F166</f>
-        <v>0</v>
-      </c>
-      <c r="H166" s="13">
-        <f>IF(A166="F",1,0)*F166</f>
-        <v>0</v>
-      </c>
-      <c r="I166" s="16">
-        <f>E166/D166</f>
-        <v>775.86206896551721</v>
-      </c>
-      <c r="J166" s="17">
-        <f>E166*F166</f>
-        <v>0</v>
-      </c>
-      <c r="K166" s="13">
-        <f>F166*D166</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" ht="16">
-      <c r="A167" t="s">
-        <v>0</v>
-      </c>
-      <c r="B167" t="s">
-        <v>448</v>
-      </c>
-      <c r="C167">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="D167">
-        <v>5.6</v>
-      </c>
-      <c r="E167" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F167" s="15">
-        <v>0</v>
-      </c>
-      <c r="G167" s="13">
-        <f>IF(A167="G",1,0)*F167</f>
-        <v>0</v>
-      </c>
-      <c r="H167" s="13">
-        <f>IF(A167="F",1,0)*F167</f>
-        <v>0</v>
-      </c>
-      <c r="I167" s="16">
-        <f>E167/D167</f>
-        <v>803.57142857142867</v>
-      </c>
-      <c r="J167" s="17">
-        <f>E167*F167</f>
-        <v>0</v>
-      </c>
-      <c r="K167" s="13">
-        <f>F167*D167</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" ht="16">
-      <c r="A168" t="s">
-        <v>0</v>
-      </c>
-      <c r="B168" t="s">
-        <v>530</v>
-      </c>
-      <c r="C168">
-        <v>5.49</v>
-      </c>
-      <c r="D168">
-        <v>5.58</v>
-      </c>
-      <c r="E168" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F168" s="15">
-        <v>0</v>
-      </c>
-      <c r="G168" s="13">
-        <f>IF(A168="G",1,0)*F168</f>
-        <v>0</v>
-      </c>
-      <c r="H168" s="13">
-        <f>IF(A168="F",1,0)*F168</f>
-        <v>0</v>
-      </c>
-      <c r="I168" s="16">
-        <f>E168/D168</f>
-        <v>806.45161290322585</v>
-      </c>
-      <c r="J168" s="17">
-        <f>E168*F168</f>
-        <v>0</v>
-      </c>
-      <c r="K168" s="13">
-        <f>F168*D168</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" ht="16">
-      <c r="A169" t="s">
-        <v>3</v>
-      </c>
-      <c r="B169" t="s">
-        <v>461</v>
-      </c>
-      <c r="C169">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="D169">
-        <v>5.58</v>
-      </c>
-      <c r="E169" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F169" s="15">
-        <v>0</v>
-      </c>
-      <c r="G169" s="13">
-        <f>IF(A169="G",1,0)*F169</f>
-        <v>0</v>
-      </c>
-      <c r="H169" s="13">
-        <f>IF(A169="F",1,0)*F169</f>
-        <v>0</v>
-      </c>
-      <c r="I169" s="16">
-        <f>E169/D169</f>
-        <v>806.45161290322585</v>
-      </c>
-      <c r="J169" s="17">
-        <f>E169*F169</f>
-        <v>0</v>
-      </c>
-      <c r="K169" s="13">
-        <f>F169*D169</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" ht="16">
-      <c r="A170" t="s">
-        <v>3</v>
-      </c>
-      <c r="B170" t="s">
-        <v>573</v>
-      </c>
-      <c r="C170">
-        <v>6.29</v>
-      </c>
-      <c r="D170">
-        <v>5.3</v>
-      </c>
-      <c r="E170" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F170" s="15">
-        <v>0</v>
-      </c>
-      <c r="G170" s="13">
-        <f>IF(A170="G",1,0)*F170</f>
-        <v>0</v>
-      </c>
-      <c r="H170" s="13">
-        <f>IF(A170="F",1,0)*F170</f>
-        <v>0</v>
-      </c>
-      <c r="I170" s="16">
-        <f>E170/D170</f>
-        <v>849.05660377358492</v>
-      </c>
-      <c r="J170" s="17">
-        <f>E170*F170</f>
-        <v>0</v>
-      </c>
-      <c r="K170" s="13">
-        <f>F170*D170</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" ht="16">
-      <c r="A171" t="s">
-        <v>0</v>
-      </c>
-      <c r="B171" t="s">
-        <v>527</v>
-      </c>
-      <c r="C171">
-        <v>4.63</v>
-      </c>
-      <c r="D171">
-        <v>5.23</v>
-      </c>
-      <c r="E171" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F171" s="15">
-        <v>0</v>
-      </c>
-      <c r="G171" s="13">
-        <f>IF(A171="G",1,0)*F171</f>
-        <v>0</v>
-      </c>
-      <c r="H171" s="13">
-        <f>IF(A171="F",1,0)*F171</f>
-        <v>0</v>
-      </c>
-      <c r="I171" s="16">
-        <f>E171/D171</f>
-        <v>860.42065009560224</v>
-      </c>
-      <c r="J171" s="17">
-        <f>E171*F171</f>
-        <v>0</v>
-      </c>
-      <c r="K171" s="13">
-        <f>F171*D171</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" ht="16">
-      <c r="A172" t="s">
-        <v>3</v>
-      </c>
-      <c r="B172" t="s">
-        <v>464</v>
-      </c>
-      <c r="C172">
-        <v>4.29</v>
-      </c>
-      <c r="D172">
-        <v>5.18</v>
-      </c>
-      <c r="E172" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F172" s="15">
-        <v>0</v>
-      </c>
-      <c r="G172" s="13">
-        <f>IF(A172="G",1,0)*F172</f>
-        <v>0</v>
-      </c>
-      <c r="H172" s="13">
-        <f>IF(A172="F",1,0)*F172</f>
-        <v>0</v>
-      </c>
-      <c r="I172" s="16">
-        <f>E172/D172</f>
-        <v>868.72586872586874</v>
-      </c>
-      <c r="J172" s="17">
-        <f>E172*F172</f>
-        <v>0</v>
-      </c>
-      <c r="K172" s="13">
-        <f>F172*D172</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" ht="16">
-      <c r="A173" t="s">
-        <v>3</v>
-      </c>
-      <c r="B173" t="s">
-        <v>563</v>
-      </c>
-      <c r="C173">
-        <v>5.74</v>
-      </c>
-      <c r="D173">
-        <v>5.17</v>
-      </c>
-      <c r="E173" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F173" s="15">
-        <v>0</v>
-      </c>
-      <c r="G173" s="13">
-        <f>IF(A173="G",1,0)*F173</f>
-        <v>0</v>
-      </c>
-      <c r="H173" s="13">
-        <f>IF(A173="F",1,0)*F173</f>
-        <v>0</v>
-      </c>
-      <c r="I173" s="16">
-        <f>E173/D173</f>
-        <v>870.40618955512571</v>
-      </c>
-      <c r="J173" s="17">
-        <f>E173*F173</f>
-        <v>0</v>
-      </c>
-      <c r="K173" s="13">
-        <f>F173*D173</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" ht="16">
-      <c r="A174" t="s">
-        <v>0</v>
-      </c>
-      <c r="B174" t="s">
-        <v>453</v>
-      </c>
-      <c r="C174">
-        <v>3.17</v>
-      </c>
-      <c r="D174">
-        <v>5.09</v>
-      </c>
-      <c r="E174" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F174" s="15">
-        <v>0</v>
-      </c>
-      <c r="G174" s="13">
-        <f>IF(A174="G",1,0)*F174</f>
-        <v>0</v>
-      </c>
-      <c r="H174" s="13">
-        <f>IF(A174="F",1,0)*F174</f>
-        <v>0</v>
-      </c>
-      <c r="I174" s="16">
-        <f>E174/D174</f>
-        <v>884.08644400785852</v>
-      </c>
-      <c r="J174" s="17">
-        <f>E174*F174</f>
-        <v>0</v>
-      </c>
-      <c r="K174" s="13">
-        <f>F174*D174</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" ht="16">
-      <c r="A175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B175" t="s">
-        <v>457</v>
-      </c>
-      <c r="C175">
-        <v>4.71</v>
-      </c>
-      <c r="D175">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="E175" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F175" s="15">
-        <v>0</v>
-      </c>
-      <c r="G175" s="13">
-        <f>IF(A175="G",1,0)*F175</f>
-        <v>0</v>
-      </c>
-      <c r="H175" s="13">
-        <f>IF(A175="F",1,0)*F175</f>
-        <v>0</v>
-      </c>
-      <c r="I175" s="16">
-        <f>E175/D175</f>
-        <v>889.32806324110675</v>
-      </c>
-      <c r="J175" s="17">
-        <f>E175*F175</f>
-        <v>0</v>
-      </c>
-      <c r="K175" s="13">
-        <f>F175*D175</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" ht="16">
-      <c r="A176" t="s">
-        <v>0</v>
-      </c>
-      <c r="B176" t="s">
-        <v>462</v>
-      </c>
-      <c r="C176">
-        <v>6.85</v>
-      </c>
-      <c r="D176">
-        <v>4.99</v>
-      </c>
-      <c r="E176" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F176" s="15">
-        <v>0</v>
-      </c>
-      <c r="G176" s="13">
-        <f>IF(A176="G",1,0)*F176</f>
-        <v>0</v>
-      </c>
-      <c r="H176" s="13">
-        <f>IF(A176="F",1,0)*F176</f>
-        <v>0</v>
-      </c>
-      <c r="I176" s="16">
-        <f>E176/D176</f>
-        <v>901.80360721442878</v>
-      </c>
-      <c r="J176" s="17">
-        <f>E176*F176</f>
-        <v>0</v>
-      </c>
-      <c r="K176" s="13">
-        <f>F176*D176</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" ht="16">
-      <c r="A177" t="s">
-        <v>3</v>
-      </c>
-      <c r="B177" t="s">
-        <v>465</v>
-      </c>
-      <c r="C177">
-        <v>5.03</v>
-      </c>
-      <c r="D177">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="E177" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F177" s="15">
-        <v>0</v>
-      </c>
-      <c r="G177" s="13">
-        <f>IF(A177="G",1,0)*F177</f>
-        <v>0</v>
-      </c>
-      <c r="H177" s="13">
-        <f>IF(A177="F",1,0)*F177</f>
-        <v>0</v>
-      </c>
-      <c r="I177" s="16">
-        <f>E177/D177</f>
-        <v>925.92592592592587</v>
-      </c>
-      <c r="J177" s="17">
-        <f>E177*F177</f>
-        <v>0</v>
-      </c>
-      <c r="K177" s="13">
-        <f>F177*D177</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" ht="16">
-      <c r="A178" t="s">
-        <v>0</v>
-      </c>
-      <c r="B178" t="s">
-        <v>444</v>
-      </c>
-      <c r="C178">
-        <v>4.46</v>
-      </c>
-      <c r="D178">
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="E178" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F178" s="15">
-        <v>0</v>
-      </c>
-      <c r="G178" s="13">
-        <f>IF(A178="G",1,0)*F178</f>
-        <v>0</v>
-      </c>
-      <c r="H178" s="13">
-        <f>IF(A178="F",1,0)*F178</f>
-        <v>0</v>
-      </c>
-      <c r="I178" s="16">
-        <f>E178/D178</f>
-        <v>927.83505154639181</v>
-      </c>
-      <c r="J178" s="17">
-        <f>E178*F178</f>
-        <v>0</v>
-      </c>
-      <c r="K178" s="13">
-        <f>F178*D178</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" ht="16">
-      <c r="A179" t="s">
-        <v>3</v>
-      </c>
-      <c r="B179" t="s">
-        <v>542</v>
-      </c>
-      <c r="C179">
-        <v>2.8</v>
-      </c>
-      <c r="D179">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="E179" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F179" s="15">
-        <v>0</v>
-      </c>
-      <c r="G179" s="13">
-        <f>IF(A179="G",1,0)*F179</f>
-        <v>0</v>
-      </c>
-      <c r="H179" s="13">
-        <f>IF(A179="F",1,0)*F179</f>
-        <v>0</v>
-      </c>
-      <c r="I179" s="16">
-        <f>E179/D179</f>
-        <v>951.37420718816054</v>
-      </c>
-      <c r="J179" s="17">
-        <f>E179*F179</f>
-        <v>0</v>
-      </c>
-      <c r="K179" s="13">
-        <f>F179*D179</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" ht="16">
-      <c r="A180" t="s">
-        <v>3</v>
-      </c>
-      <c r="B180" t="s">
-        <v>579</v>
-      </c>
-      <c r="C180">
-        <v>6.73</v>
-      </c>
-      <c r="D180">
-        <v>4.53</v>
-      </c>
-      <c r="E180" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F180" s="15">
-        <v>0</v>
-      </c>
-      <c r="G180" s="13">
-        <f>IF(A180="G",1,0)*F180</f>
-        <v>0</v>
-      </c>
-      <c r="H180" s="13">
-        <f>IF(A180="F",1,0)*F180</f>
-        <v>0</v>
-      </c>
-      <c r="I180" s="16">
-        <f>E180/D180</f>
-        <v>993.37748344370857</v>
-      </c>
-      <c r="J180" s="17">
-        <f>E180*F180</f>
-        <v>0</v>
-      </c>
-      <c r="K180" s="13">
-        <f>F180*D180</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" ht="16">
-      <c r="A181" t="s">
-        <v>3</v>
-      </c>
-      <c r="B181" t="s">
-        <v>454</v>
-      </c>
-      <c r="C181">
-        <v>6.46</v>
-      </c>
-      <c r="D181">
-        <v>4.51</v>
-      </c>
-      <c r="E181" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F181" s="15">
-        <v>0</v>
-      </c>
-      <c r="G181" s="13">
-        <f>IF(A181="G",1,0)*F181</f>
-        <v>0</v>
-      </c>
-      <c r="H181" s="13">
-        <f>IF(A181="F",1,0)*F181</f>
-        <v>0</v>
-      </c>
-      <c r="I181" s="16">
-        <f>E181/D181</f>
-        <v>997.78270509977835</v>
-      </c>
-      <c r="J181" s="17">
-        <f>E181*F181</f>
-        <v>0</v>
-      </c>
-      <c r="K181" s="13">
-        <f>F181*D181</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" ht="16">
-      <c r="A182" t="s">
-        <v>0</v>
-      </c>
-      <c r="B182" t="s">
-        <v>528</v>
-      </c>
-      <c r="C182">
-        <v>5.8</v>
-      </c>
-      <c r="D182">
-        <v>4.26</v>
-      </c>
-      <c r="E182" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F182" s="15">
-        <v>0</v>
-      </c>
-      <c r="G182" s="13">
-        <f>IF(A182="G",1,0)*F182</f>
-        <v>0</v>
-      </c>
-      <c r="H182" s="13">
-        <f>IF(A182="F",1,0)*F182</f>
-        <v>0</v>
-      </c>
-      <c r="I182" s="16">
-        <f>E182/D182</f>
-        <v>1056.3380281690143</v>
-      </c>
-      <c r="J182" s="17">
-        <f>E182*F182</f>
-        <v>0</v>
-      </c>
-      <c r="K182" s="13">
-        <f>F182*D182</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" ht="16">
-      <c r="A183" t="s">
-        <v>3</v>
-      </c>
-      <c r="B183" t="s">
-        <v>447</v>
-      </c>
-      <c r="C183">
-        <v>6.17</v>
-      </c>
-      <c r="D183">
-        <v>4.26</v>
-      </c>
-      <c r="E183" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F183" s="15">
-        <v>0</v>
-      </c>
-      <c r="G183" s="13">
-        <f>IF(A183="G",1,0)*F183</f>
-        <v>0</v>
-      </c>
-      <c r="H183" s="13">
-        <f>IF(A183="F",1,0)*F183</f>
-        <v>0</v>
-      </c>
-      <c r="I183" s="16">
-        <f>E183/D183</f>
-        <v>1056.3380281690143</v>
-      </c>
-      <c r="J183" s="17">
-        <f>E183*F183</f>
-        <v>0</v>
-      </c>
-      <c r="K183" s="13">
-        <f>F183*D183</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" ht="16">
-      <c r="A184" t="s">
-        <v>0</v>
-      </c>
-      <c r="B184" t="s">
-        <v>567</v>
-      </c>
-      <c r="C184">
-        <v>3.79</v>
-      </c>
-      <c r="D184">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="E184" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F184" s="15">
-        <v>0</v>
-      </c>
-      <c r="G184" s="13">
-        <f>IF(A184="G",1,0)*F184</f>
-        <v>0</v>
-      </c>
-      <c r="H184" s="13">
-        <f>IF(A184="F",1,0)*F184</f>
-        <v>0</v>
-      </c>
-      <c r="I184" s="16">
-        <f>E184/D184</f>
-        <v>1063.8297872340424</v>
-      </c>
-      <c r="J184" s="17">
-        <f>E184*F184</f>
-        <v>0</v>
-      </c>
-      <c r="K184" s="13">
-        <f>F184*D184</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" ht="16">
-      <c r="A185" t="s">
-        <v>3</v>
-      </c>
-      <c r="B185" t="s">
-        <v>450</v>
-      </c>
-      <c r="C185">
-        <v>5.41</v>
-      </c>
-      <c r="D185">
-        <v>4.18</v>
-      </c>
-      <c r="E185" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F185" s="15">
-        <v>0</v>
-      </c>
-      <c r="G185" s="13">
-        <f>IF(A185="G",1,0)*F185</f>
-        <v>0</v>
-      </c>
-      <c r="H185" s="13">
-        <f>IF(A185="F",1,0)*F185</f>
-        <v>0</v>
-      </c>
-      <c r="I185" s="16">
-        <f>E185/D185</f>
-        <v>1076.5550239234451</v>
-      </c>
-      <c r="J185" s="17">
-        <f>E185*F185</f>
-        <v>0</v>
-      </c>
-      <c r="K185" s="13">
-        <f>F185*D185</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" ht="16">
-      <c r="A186" t="s">
-        <v>3</v>
-      </c>
-      <c r="B186" t="s">
-        <v>451</v>
-      </c>
-      <c r="C186">
-        <v>3.89</v>
-      </c>
-      <c r="D186">
-        <v>4.12</v>
-      </c>
-      <c r="E186" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F186" s="15">
-        <v>0</v>
-      </c>
-      <c r="G186" s="13">
-        <f>IF(A186="G",1,0)*F186</f>
-        <v>0</v>
-      </c>
-      <c r="H186" s="13">
-        <f>IF(A186="F",1,0)*F186</f>
-        <v>0</v>
-      </c>
-      <c r="I186" s="16">
-        <f>E186/D186</f>
-        <v>1092.2330097087379</v>
-      </c>
-      <c r="J186" s="17">
-        <f>E186*F186</f>
-        <v>0</v>
-      </c>
-      <c r="K186" s="13">
-        <f>F186*D186</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" ht="16">
-      <c r="A187" t="s">
-        <v>3</v>
-      </c>
-      <c r="B187" t="s">
-        <v>564</v>
-      </c>
-      <c r="C187">
-        <v>5.67</v>
-      </c>
-      <c r="D187">
-        <v>4.07</v>
-      </c>
-      <c r="E187" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F187" s="15">
-        <v>0</v>
-      </c>
-      <c r="G187" s="13">
-        <f>IF(A187="G",1,0)*F187</f>
-        <v>0</v>
-      </c>
-      <c r="H187" s="13">
-        <f>IF(A187="F",1,0)*F187</f>
-        <v>0</v>
-      </c>
-      <c r="I187" s="16">
-        <f>E187/D187</f>
-        <v>1105.6511056511056</v>
-      </c>
-      <c r="J187" s="17">
-        <f>E187*F187</f>
-        <v>0</v>
-      </c>
-      <c r="K187" s="13">
-        <f>F187*D187</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" ht="16">
-      <c r="A188" t="s">
-        <v>0</v>
-      </c>
-      <c r="B188" t="s">
-        <v>532</v>
-      </c>
-      <c r="C188">
-        <v>3.64</v>
-      </c>
-      <c r="D188">
-        <v>3.97</v>
-      </c>
-      <c r="E188" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F188" s="15">
-        <v>0</v>
-      </c>
-      <c r="G188" s="13">
-        <f>IF(A188="G",1,0)*F188</f>
-        <v>0</v>
-      </c>
-      <c r="H188" s="13">
-        <f>IF(A188="F",1,0)*F188</f>
-        <v>0</v>
-      </c>
-      <c r="I188" s="16">
-        <f>E188/D188</f>
-        <v>1133.5012594458437</v>
-      </c>
-      <c r="J188" s="17">
-        <f>E188*F188</f>
-        <v>0</v>
-      </c>
-      <c r="K188" s="13">
-        <f>F188*D188</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" ht="16">
-      <c r="A189" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" t="s">
-        <v>467</v>
-      </c>
-      <c r="C189">
-        <v>6</v>
-      </c>
-      <c r="D189">
-        <v>3.92</v>
-      </c>
-      <c r="E189" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F189" s="15">
-        <v>0</v>
-      </c>
-      <c r="G189" s="13">
-        <f>IF(A189="G",1,0)*F189</f>
-        <v>0</v>
-      </c>
-      <c r="H189" s="13">
-        <f>IF(A189="F",1,0)*F189</f>
-        <v>0</v>
-      </c>
-      <c r="I189" s="16">
-        <f>E189/D189</f>
-        <v>1147.9591836734694</v>
-      </c>
-      <c r="J189" s="17">
-        <f>E189*F189</f>
-        <v>0</v>
-      </c>
-      <c r="K189" s="13">
-        <f>F189*D189</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" ht="16">
-      <c r="A190" t="s">
-        <v>3</v>
-      </c>
-      <c r="B190" t="s">
-        <v>557</v>
-      </c>
-      <c r="C190">
-        <v>3.74</v>
-      </c>
-      <c r="D190">
-        <v>3.8</v>
-      </c>
-      <c r="E190" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F190" s="15">
-        <v>0</v>
-      </c>
-      <c r="G190" s="13">
-        <f>IF(A190="G",1,0)*F190</f>
-        <v>0</v>
-      </c>
-      <c r="H190" s="13">
-        <f>IF(A190="F",1,0)*F190</f>
-        <v>0</v>
-      </c>
-      <c r="I190" s="16">
-        <f>E190/D190</f>
-        <v>1184.2105263157896</v>
-      </c>
-      <c r="J190" s="17">
-        <f>E190*F190</f>
-        <v>0</v>
-      </c>
-      <c r="K190" s="13">
-        <f>F190*D190</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" ht="16">
-      <c r="A191" t="s">
-        <v>0</v>
-      </c>
-      <c r="B191" t="s">
-        <v>540</v>
-      </c>
-      <c r="C191">
-        <v>2.12</v>
-      </c>
-      <c r="D191">
-        <v>3.72</v>
-      </c>
-      <c r="E191" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F191" s="15">
-        <v>0</v>
-      </c>
-      <c r="G191" s="13">
-        <f>IF(A191="G",1,0)*F191</f>
-        <v>0</v>
-      </c>
-      <c r="H191" s="13">
-        <f>IF(A191="F",1,0)*F191</f>
-        <v>0</v>
-      </c>
-      <c r="I191" s="16">
-        <f>E191/D191</f>
-        <v>1209.6774193548385</v>
-      </c>
-      <c r="J191" s="17">
-        <f>E191*F191</f>
-        <v>0</v>
-      </c>
-      <c r="K191" s="13">
-        <f>F191*D191</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" ht="16">
-      <c r="A192" t="s">
-        <v>3</v>
-      </c>
-      <c r="B192" t="s">
-        <v>131</v>
-      </c>
-      <c r="C192">
-        <v>3.54</v>
-      </c>
-      <c r="D192">
-        <v>3.64</v>
-      </c>
-      <c r="E192" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F192" s="15">
-        <v>0</v>
-      </c>
-      <c r="G192" s="13">
-        <f>IF(A192="G",1,0)*F192</f>
-        <v>0</v>
-      </c>
-      <c r="H192" s="13">
-        <f>IF(A192="F",1,0)*F192</f>
-        <v>0</v>
-      </c>
-      <c r="I192" s="16">
-        <f>E192/D192</f>
-        <v>1236.2637362637363</v>
-      </c>
-      <c r="J192" s="17">
-        <f>E192*F192</f>
-        <v>0</v>
-      </c>
-      <c r="K192" s="13">
-        <f>F192*D192</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" ht="16">
-      <c r="A193" t="s">
-        <v>0</v>
-      </c>
-      <c r="B193" t="s">
-        <v>449</v>
-      </c>
-      <c r="C193">
-        <v>5.25</v>
-      </c>
-      <c r="D193">
-        <v>3.62</v>
-      </c>
-      <c r="E193" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F193" s="15">
-        <v>0</v>
-      </c>
-      <c r="G193" s="13">
-        <f>IF(A193="G",1,0)*F193</f>
-        <v>0</v>
-      </c>
-      <c r="H193" s="13">
-        <f>IF(A193="F",1,0)*F193</f>
-        <v>0</v>
-      </c>
-      <c r="I193" s="16">
-        <f>E193/D193</f>
-        <v>1243.0939226519336</v>
-      </c>
-      <c r="J193" s="17">
-        <f>E193*F193</f>
-        <v>0</v>
-      </c>
-      <c r="K193" s="13">
-        <f>F193*D193</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" ht="16">
-      <c r="A194" t="s">
-        <v>0</v>
-      </c>
-      <c r="B194" t="s">
-        <v>570</v>
-      </c>
-      <c r="C194">
-        <v>3.83</v>
-      </c>
-      <c r="D194">
-        <v>3.49</v>
-      </c>
-      <c r="E194" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F194" s="15">
-        <v>0</v>
-      </c>
-      <c r="G194" s="13">
-        <f>IF(A194="G",1,0)*F194</f>
-        <v>0</v>
-      </c>
-      <c r="H194" s="13">
-        <f>IF(A194="F",1,0)*F194</f>
-        <v>0</v>
-      </c>
-      <c r="I194" s="16">
-        <f>E194/D194</f>
-        <v>1289.3982808022922</v>
-      </c>
-      <c r="J194" s="17">
-        <f>E194*F194</f>
-        <v>0</v>
-      </c>
-      <c r="K194" s="13">
-        <f>F194*D194</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" ht="16">
-      <c r="A195" t="s">
-        <v>3</v>
-      </c>
-      <c r="B195" t="s">
-        <v>548</v>
-      </c>
-      <c r="C195">
-        <v>1.9</v>
-      </c>
-      <c r="D195">
-        <v>3.36</v>
-      </c>
-      <c r="E195" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F195" s="15">
-        <v>0</v>
-      </c>
-      <c r="G195" s="13">
-        <f>IF(A195="G",1,0)*F195</f>
-        <v>0</v>
-      </c>
-      <c r="H195" s="13">
-        <f>IF(A195="F",1,0)*F195</f>
-        <v>0</v>
-      </c>
-      <c r="I195" s="16">
-        <f>E195/D195</f>
-        <v>1339.2857142857144</v>
-      </c>
-      <c r="J195" s="17">
-        <f>E195*F195</f>
-        <v>0</v>
-      </c>
-      <c r="K195" s="13">
-        <f>F195*D195</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" ht="16">
-      <c r="A196" t="s">
-        <v>3</v>
-      </c>
-      <c r="B196" t="s">
-        <v>572</v>
-      </c>
-      <c r="C196">
-        <v>4.08</v>
-      </c>
-      <c r="D196">
-        <v>3.29</v>
-      </c>
-      <c r="E196" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F196" s="15">
-        <v>0</v>
-      </c>
-      <c r="G196" s="13">
-        <f>IF(A196="G",1,0)*F196</f>
-        <v>0</v>
-      </c>
-      <c r="H196" s="13">
-        <f>IF(A196="F",1,0)*F196</f>
-        <v>0</v>
-      </c>
-      <c r="I196" s="16">
-        <f>E196/D196</f>
-        <v>1367.7811550151976</v>
-      </c>
-      <c r="J196" s="17">
-        <f>E196*F196</f>
-        <v>0</v>
-      </c>
-      <c r="K196" s="13">
-        <f>F196*D196</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" ht="16">
-      <c r="A197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" t="s">
-        <v>558</v>
-      </c>
-      <c r="C197">
-        <v>2.93</v>
-      </c>
-      <c r="D197">
-        <v>3.17</v>
-      </c>
-      <c r="E197" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F197" s="15">
-        <v>0</v>
-      </c>
-      <c r="G197" s="13">
-        <f>IF(A197="G",1,0)*F197</f>
-        <v>0</v>
-      </c>
-      <c r="H197" s="13">
-        <f>IF(A197="F",1,0)*F197</f>
-        <v>0</v>
-      </c>
-      <c r="I197" s="16">
-        <f>E197/D197</f>
-        <v>1419.5583596214512</v>
-      </c>
-      <c r="J197" s="17">
-        <f>E197*F197</f>
-        <v>0</v>
-      </c>
-      <c r="K197" s="13">
-        <f>F197*D197</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" ht="16">
-      <c r="A198" t="s">
-        <v>0</v>
-      </c>
-      <c r="B198" t="s">
-        <v>529</v>
-      </c>
-      <c r="C198">
-        <v>2.35</v>
-      </c>
-      <c r="D198">
-        <v>3.1</v>
-      </c>
-      <c r="E198" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F198" s="15">
-        <v>0</v>
-      </c>
-      <c r="G198" s="13">
-        <f>IF(A198="G",1,0)*F198</f>
-        <v>0</v>
-      </c>
-      <c r="H198" s="13">
-        <f>IF(A198="F",1,0)*F198</f>
-        <v>0</v>
-      </c>
-      <c r="I198" s="16">
-        <f>E198/D198</f>
-        <v>1451.6129032258063</v>
-      </c>
-      <c r="J198" s="17">
-        <f>E198*F198</f>
-        <v>0</v>
-      </c>
-      <c r="K198" s="13">
-        <f>F198*D198</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" ht="16">
-      <c r="A199" t="s">
-        <v>3</v>
-      </c>
-      <c r="B199" t="s">
-        <v>443</v>
-      </c>
-      <c r="C199">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D199">
-        <v>3.1</v>
-      </c>
-      <c r="E199" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F199" s="15">
-        <v>0</v>
-      </c>
-      <c r="G199" s="13">
-        <f>IF(A199="G",1,0)*F199</f>
-        <v>0</v>
-      </c>
-      <c r="H199" s="13">
-        <f>IF(A199="F",1,0)*F199</f>
-        <v>0</v>
-      </c>
-      <c r="I199" s="16">
-        <f>E199/D199</f>
-        <v>1451.6129032258063</v>
-      </c>
-      <c r="J199" s="17">
-        <f>E199*F199</f>
-        <v>0</v>
-      </c>
-      <c r="K199" s="13">
-        <f>F199*D199</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" ht="16">
-      <c r="A200" t="s">
-        <v>0</v>
-      </c>
-      <c r="B200" t="s">
-        <v>571</v>
-      </c>
-      <c r="C200">
-        <v>3.3</v>
-      </c>
-      <c r="D200">
-        <v>3.05</v>
-      </c>
-      <c r="E200" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F200" s="15">
-        <v>0</v>
-      </c>
-      <c r="G200" s="13">
-        <f>IF(A200="G",1,0)*F200</f>
-        <v>0</v>
-      </c>
-      <c r="H200" s="13">
-        <f>IF(A200="F",1,0)*F200</f>
-        <v>0</v>
-      </c>
-      <c r="I200" s="16">
-        <f>E200/D200</f>
-        <v>1475.4098360655739</v>
-      </c>
-      <c r="J200" s="17">
-        <f>E200*F200</f>
-        <v>0</v>
-      </c>
-      <c r="K200" s="13">
-        <f>F200*D200</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11">
+    <row r="124" spans="1:11">
+      <c r="D124" s="3"/>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="D127" s="3"/>
+    </row>
+    <row r="130" spans="4:4">
+      <c r="D130" s="3"/>
+    </row>
+    <row r="133" spans="4:4">
+      <c r="D133" s="3"/>
+    </row>
+    <row r="136" spans="4:4">
+      <c r="D136" s="3"/>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" s="3"/>
+    </row>
+    <row r="142" spans="4:4">
+      <c r="D142" s="3"/>
+    </row>
+    <row r="145" spans="4:4">
+      <c r="D145" s="3"/>
+    </row>
+    <row r="148" spans="4:4">
+      <c r="D148" s="3"/>
+    </row>
+    <row r="151" spans="4:4">
+      <c r="D151" s="3"/>
+    </row>
+    <row r="154" spans="4:4">
+      <c r="D154" s="3"/>
+    </row>
+    <row r="157" spans="4:4">
+      <c r="D157" s="3"/>
+    </row>
+    <row r="160" spans="4:4">
+      <c r="D160" s="3"/>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" s="3"/>
+    </row>
+    <row r="166" spans="4:4">
+      <c r="D166" s="3"/>
+    </row>
+    <row r="169" spans="4:4">
+      <c r="D169" s="3"/>
+    </row>
+    <row r="172" spans="4:4">
+      <c r="D172" s="3"/>
+    </row>
+    <row r="175" spans="4:4">
+      <c r="D175" s="3"/>
+    </row>
+    <row r="178" spans="4:4">
+      <c r="D178" s="3"/>
+    </row>
+    <row r="181" spans="4:4">
+      <c r="D181" s="3"/>
+    </row>
+    <row r="184" spans="4:4">
+      <c r="D184" s="3"/>
+    </row>
+    <row r="187" spans="4:4">
+      <c r="D187" s="3"/>
+    </row>
+    <row r="190" spans="4:4">
+      <c r="D190" s="3"/>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" s="3"/>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" s="3"/>
+    </row>
+    <row r="199" spans="4:4">
+      <c r="D199" s="3"/>
+    </row>
+    <row r="202" spans="4:4">
       <c r="D202" s="3"/>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="4:4">
       <c r="D205" s="3"/>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="4:4">
       <c r="D208" s="3"/>
     </row>
     <row r="211" spans="4:4">
@@ -11043,87 +7776,9 @@
     <row r="496" spans="4:4">
       <c r="D496" s="3"/>
     </row>
-    <row r="499" spans="4:4">
-      <c r="D499" s="3"/>
-    </row>
-    <row r="502" spans="4:4">
-      <c r="D502" s="3"/>
-    </row>
-    <row r="505" spans="4:4">
-      <c r="D505" s="3"/>
-    </row>
-    <row r="508" spans="4:4">
-      <c r="D508" s="3"/>
-    </row>
-    <row r="511" spans="4:4">
-      <c r="D511" s="3"/>
-    </row>
-    <row r="514" spans="4:4">
-      <c r="D514" s="3"/>
-    </row>
-    <row r="517" spans="4:4">
-      <c r="D517" s="3"/>
-    </row>
-    <row r="520" spans="4:4">
-      <c r="D520" s="3"/>
-    </row>
-    <row r="523" spans="4:4">
-      <c r="D523" s="3"/>
-    </row>
-    <row r="526" spans="4:4">
-      <c r="D526" s="3"/>
-    </row>
-    <row r="529" spans="4:4">
-      <c r="D529" s="3"/>
-    </row>
-    <row r="532" spans="4:4">
-      <c r="D532" s="3"/>
-    </row>
-    <row r="535" spans="4:4">
-      <c r="D535" s="3"/>
-    </row>
-    <row r="538" spans="4:4">
-      <c r="D538" s="3"/>
-    </row>
-    <row r="541" spans="4:4">
-      <c r="D541" s="3"/>
-    </row>
-    <row r="544" spans="4:4">
-      <c r="D544" s="3"/>
-    </row>
-    <row r="547" spans="4:4">
-      <c r="D547" s="3"/>
-    </row>
-    <row r="550" spans="4:4">
-      <c r="D550" s="3"/>
-    </row>
-    <row r="553" spans="4:4">
-      <c r="D553" s="3"/>
-    </row>
-    <row r="556" spans="4:4">
-      <c r="D556" s="3"/>
-    </row>
-    <row r="559" spans="4:4">
-      <c r="D559" s="3"/>
-    </row>
-    <row r="562" spans="4:4">
-      <c r="D562" s="3"/>
-    </row>
-    <row r="565" spans="4:4">
-      <c r="D565" s="3"/>
-    </row>
-    <row r="568" spans="4:4">
-      <c r="D568" s="3"/>
-    </row>
-    <row r="571" spans="4:4">
-      <c r="D571" s="3"/>
-    </row>
-    <row r="574" spans="4:4">
-      <c r="D574" s="3"/>
-    </row>
   </sheetData>
-  <sortState ref="A2:K625">
-    <sortCondition ref="I2:I625"/>
+  <sortState ref="A2:K122">
+    <sortCondition descending="1" ref="F5"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
